--- a/artfynd/A 71374-2021 artfynd.xlsx
+++ b/artfynd/A 71374-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121590851</v>
+        <v>121590869</v>
       </c>
       <c r="B2" t="n">
-        <v>91990</v>
+        <v>77993</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>6437</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730803</v>
+        <v>730756</v>
       </c>
       <c r="R2" t="n">
-        <v>7358733</v>
+        <v>7358818</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121590856</v>
+        <v>121590859</v>
       </c>
       <c r="B3" t="n">
-        <v>97059</v>
+        <v>77541</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6487</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730873</v>
+        <v>730851</v>
       </c>
       <c r="R3" t="n">
-        <v>7358715</v>
+        <v>7358729</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -861,6 +866,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På grov gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121590868</v>
+        <v>121590879</v>
       </c>
       <c r="B4" t="n">
-        <v>79227</v>
+        <v>92012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,26 +913,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730799</v>
+        <v>730730</v>
       </c>
       <c r="R4" t="n">
-        <v>7358812</v>
+        <v>7358824</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -967,11 +977,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121590879</v>
+        <v>121590840</v>
       </c>
       <c r="B5" t="n">
-        <v>92012</v>
+        <v>97059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,30 +1015,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2059</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1042,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730730</v>
+        <v>731001</v>
       </c>
       <c r="R5" t="n">
-        <v>7358824</v>
+        <v>7358693</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1104,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121590874</v>
+        <v>121590845</v>
       </c>
       <c r="B6" t="n">
-        <v>91990</v>
+        <v>91988</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,26 +1125,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1148,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730724</v>
+        <v>730764</v>
       </c>
       <c r="R6" t="n">
-        <v>7358840</v>
+        <v>7358768</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121590871</v>
+        <v>121590852</v>
       </c>
       <c r="B7" t="n">
-        <v>79198</v>
+        <v>79719</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1222,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1254,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730758</v>
+        <v>730829</v>
       </c>
       <c r="R7" t="n">
-        <v>7358818</v>
+        <v>7358728</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1294,7 +1299,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121590860</v>
+        <v>121590872</v>
       </c>
       <c r="B8" t="n">
-        <v>78345</v>
+        <v>91990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,26 +1342,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1365,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730824</v>
+        <v>730741</v>
       </c>
       <c r="R8" t="n">
-        <v>7358748</v>
+        <v>7358824</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1401,11 +1406,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På grov gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121590842</v>
+        <v>121590854</v>
       </c>
       <c r="B9" t="n">
-        <v>91282</v>
+        <v>79691</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,25 +1444,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730938</v>
+        <v>730828</v>
       </c>
       <c r="R9" t="n">
-        <v>7358696</v>
+        <v>7358733</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1543,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121590853</v>
+        <v>121590843</v>
       </c>
       <c r="B10" t="n">
-        <v>79726</v>
+        <v>79719</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1559,21 +1559,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730825</v>
+        <v>730936</v>
       </c>
       <c r="R10" t="n">
-        <v>7358734</v>
+        <v>7358694</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På grov sälg</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121590863</v>
+        <v>121590873</v>
       </c>
       <c r="B11" t="n">
-        <v>97065</v>
+        <v>92012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,30 +1666,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221941</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730859</v>
+        <v>730737</v>
       </c>
       <c r="R11" t="n">
-        <v>7358837</v>
+        <v>7358829</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121590839</v>
+        <v>121590871</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>79198</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1776,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>731001</v>
+        <v>730758</v>
       </c>
       <c r="R12" t="n">
-        <v>7358729</v>
+        <v>7358818</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Mindre ex på en gammal gran</t>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121590834</v>
+        <v>121590844</v>
       </c>
       <c r="B13" t="n">
-        <v>57372</v>
+        <v>79726</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,25 +1883,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>731015</v>
+        <v>730907</v>
       </c>
       <c r="R13" t="n">
-        <v>7358724</v>
+        <v>7358717</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Födosökshack i tallöverståndare</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121590885</v>
+        <v>121590881</v>
       </c>
       <c r="B14" t="n">
-        <v>92008</v>
+        <v>89396</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1994,30 +1994,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>6276</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730757</v>
+        <v>730733</v>
       </c>
       <c r="R14" t="n">
-        <v>7358754</v>
+        <v>7358825</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121590859</v>
+        <v>121590855</v>
       </c>
       <c r="B15" t="n">
-        <v>77541</v>
+        <v>79725</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2100,25 +2100,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6487</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730851</v>
+        <v>730855</v>
       </c>
       <c r="R15" t="n">
-        <v>7358729</v>
+        <v>7358731</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2172,7 +2172,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På grov gammal kolad tallhögstubbe</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,10 +2199,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121590841</v>
+        <v>121590842</v>
       </c>
       <c r="B16" t="n">
-        <v>82393</v>
+        <v>91282</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2211,25 +2211,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>760</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730998</v>
+        <v>730938</v>
       </c>
       <c r="R16" t="n">
         <v>7358696</v>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,10 +2310,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121590852</v>
+        <v>121590863</v>
       </c>
       <c r="B17" t="n">
-        <v>79719</v>
+        <v>97065</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2326,21 +2326,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2354,10 +2354,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730829</v>
+        <v>730859</v>
       </c>
       <c r="R17" t="n">
-        <v>7358728</v>
+        <v>7358837</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2390,11 +2390,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2421,10 +2416,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121590857</v>
+        <v>121590837</v>
       </c>
       <c r="B18" t="n">
-        <v>79594</v>
+        <v>90738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2433,25 +2428,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6456</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2465,10 +2460,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730854</v>
+        <v>730955</v>
       </c>
       <c r="R18" t="n">
-        <v>7358725</v>
+        <v>7358774</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2505,7 +2500,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På granhögstubbe och -låga</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2532,10 +2527,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121590849</v>
+        <v>121590839</v>
       </c>
       <c r="B19" t="n">
-        <v>91990</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2548,26 +2543,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2576,10 +2571,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730804</v>
+        <v>731001</v>
       </c>
       <c r="R19" t="n">
-        <v>7358743</v>
+        <v>7358729</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2612,6 +2607,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Mindre ex på en gammal gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2638,10 +2638,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121590882</v>
+        <v>121590838</v>
       </c>
       <c r="B20" t="n">
-        <v>91990</v>
+        <v>82393</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2654,26 +2654,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2682,10 +2682,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730749</v>
+        <v>730995</v>
       </c>
       <c r="R20" t="n">
-        <v>7358805</v>
+        <v>7358751</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2744,7 +2744,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121590872</v>
+        <v>121590851</v>
       </c>
       <c r="B21" t="n">
         <v>91990</v>
@@ -2779,7 +2779,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730741</v>
+        <v>730803</v>
       </c>
       <c r="R21" t="n">
-        <v>7358824</v>
+        <v>7358733</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2850,10 +2850,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121590854</v>
+        <v>121590876</v>
       </c>
       <c r="B22" t="n">
-        <v>79691</v>
+        <v>92008</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2862,25 +2862,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2894,10 +2894,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730828</v>
+        <v>730724</v>
       </c>
       <c r="R22" t="n">
-        <v>7358733</v>
+        <v>7358834</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2930,11 +2930,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2961,10 +2956,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121590855</v>
+        <v>121590858</v>
       </c>
       <c r="B23" t="n">
-        <v>79725</v>
+        <v>79719</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2977,21 +2972,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3005,10 +3000,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730855</v>
+        <v>730856</v>
       </c>
       <c r="R23" t="n">
-        <v>7358731</v>
+        <v>7358724</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3045,7 +3040,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3072,10 +3067,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121590835</v>
+        <v>121590870</v>
       </c>
       <c r="B24" t="n">
-        <v>79726</v>
+        <v>77541</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3084,25 +3079,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3116,10 +3111,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730890</v>
+        <v>730756</v>
       </c>
       <c r="R24" t="n">
-        <v>7358797</v>
+        <v>7358818</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3156,7 +3151,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3183,10 +3178,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121590876</v>
+        <v>121590834</v>
       </c>
       <c r="B25" t="n">
-        <v>92008</v>
+        <v>57372</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3195,25 +3190,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3227,10 +3222,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730724</v>
+        <v>731015</v>
       </c>
       <c r="R25" t="n">
-        <v>7358834</v>
+        <v>7358724</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3263,6 +3258,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Födosökshack i tallöverståndare</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3289,10 +3289,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121590837</v>
+        <v>121590885</v>
       </c>
       <c r="B26" t="n">
-        <v>90738</v>
+        <v>92008</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3301,30 +3301,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>4366</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3333,10 +3333,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730955</v>
+        <v>730757</v>
       </c>
       <c r="R26" t="n">
-        <v>7358774</v>
+        <v>7358754</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3369,11 +3369,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På granhögstubbe och -låga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3400,10 +3395,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121590881</v>
+        <v>121590847</v>
       </c>
       <c r="B27" t="n">
-        <v>89396</v>
+        <v>91990</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3412,30 +3407,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3444,10 +3439,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730733</v>
+        <v>730811</v>
       </c>
       <c r="R27" t="n">
-        <v>7358825</v>
+        <v>7358748</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3506,10 +3501,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121590866</v>
+        <v>121590850</v>
       </c>
       <c r="B28" t="n">
-        <v>78345</v>
+        <v>91996</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3518,30 +3513,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3550,10 +3545,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730818</v>
+        <v>730806</v>
       </c>
       <c r="R28" t="n">
-        <v>7358836</v>
+        <v>7358740</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3586,11 +3581,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3617,10 +3607,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121590836</v>
+        <v>121590884</v>
       </c>
       <c r="B29" t="n">
-        <v>79719</v>
+        <v>92021</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3629,30 +3619,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>3100</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3661,10 +3651,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730893</v>
+        <v>730767</v>
       </c>
       <c r="R29" t="n">
-        <v>7358778</v>
+        <v>7358759</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3697,11 +3687,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3728,10 +3713,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121590838</v>
+        <v>121590860</v>
       </c>
       <c r="B30" t="n">
-        <v>82393</v>
+        <v>78345</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3744,21 +3729,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3772,10 +3757,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730995</v>
+        <v>730824</v>
       </c>
       <c r="R30" t="n">
-        <v>7358751</v>
+        <v>7358748</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3808,6 +3793,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På grov gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3834,10 +3824,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121590869</v>
+        <v>121590841</v>
       </c>
       <c r="B31" t="n">
-        <v>77993</v>
+        <v>82393</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3850,21 +3840,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3878,10 +3868,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730756</v>
+        <v>730998</v>
       </c>
       <c r="R31" t="n">
-        <v>7358818</v>
+        <v>7358696</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3918,7 +3908,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3945,10 +3935,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121590858</v>
+        <v>121590861</v>
       </c>
       <c r="B32" t="n">
-        <v>79719</v>
+        <v>92024</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3957,30 +3947,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6462</v>
+        <v>5449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3989,10 +3979,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730856</v>
+        <v>730810</v>
       </c>
       <c r="R32" t="n">
-        <v>7358724</v>
+        <v>7358795</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4025,11 +4015,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4056,10 +4041,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121590880</v>
+        <v>121590848</v>
       </c>
       <c r="B33" t="n">
-        <v>91996</v>
+        <v>92021</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4068,25 +4053,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4100,10 +4085,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730731</v>
+        <v>730804</v>
       </c>
       <c r="R33" t="n">
-        <v>7358821</v>
+        <v>7358743</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4162,10 +4147,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121590845</v>
+        <v>121590866</v>
       </c>
       <c r="B34" t="n">
-        <v>91988</v>
+        <v>78345</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4178,26 +4163,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4206,10 +4191,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730764</v>
+        <v>730818</v>
       </c>
       <c r="R34" t="n">
-        <v>7358768</v>
+        <v>7358836</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4242,6 +4227,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4268,10 +4258,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121590883</v>
+        <v>121590856</v>
       </c>
       <c r="B35" t="n">
-        <v>92024</v>
+        <v>97059</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4280,30 +4270,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4312,10 +4302,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730758</v>
+        <v>730873</v>
       </c>
       <c r="R35" t="n">
-        <v>7358773</v>
+        <v>7358715</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4374,10 +4364,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121590846</v>
+        <v>121590883</v>
       </c>
       <c r="B36" t="n">
-        <v>92021</v>
+        <v>92024</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4390,26 +4380,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3100</v>
+        <v>5449</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4418,10 +4408,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730810</v>
+        <v>730758</v>
       </c>
       <c r="R36" t="n">
-        <v>7358754</v>
+        <v>7358773</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4480,10 +4470,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121590844</v>
+        <v>121590868</v>
       </c>
       <c r="B37" t="n">
-        <v>79726</v>
+        <v>79227</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4492,25 +4482,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6464</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4524,10 +4514,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730907</v>
+        <v>730799</v>
       </c>
       <c r="R37" t="n">
-        <v>7358717</v>
+        <v>7358812</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4564,7 +4554,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4591,10 +4581,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121590843</v>
+        <v>121590864</v>
       </c>
       <c r="B38" t="n">
-        <v>79719</v>
+        <v>91996</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4607,26 +4597,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4635,10 +4625,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730936</v>
+        <v>730835</v>
       </c>
       <c r="R38" t="n">
-        <v>7358694</v>
+        <v>7358839</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4671,11 +4661,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4702,10 +4687,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121590848</v>
+        <v>121590882</v>
       </c>
       <c r="B39" t="n">
-        <v>92021</v>
+        <v>91990</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4718,26 +4703,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4746,10 +4731,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730804</v>
+        <v>730749</v>
       </c>
       <c r="R39" t="n">
-        <v>7358743</v>
+        <v>7358805</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4808,10 +4793,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121590850</v>
+        <v>121590846</v>
       </c>
       <c r="B40" t="n">
-        <v>91996</v>
+        <v>92021</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4820,30 +4805,30 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4852,10 +4837,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730806</v>
+        <v>730810</v>
       </c>
       <c r="R40" t="n">
-        <v>7358740</v>
+        <v>7358754</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4914,10 +4899,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121590884</v>
+        <v>121590853</v>
       </c>
       <c r="B41" t="n">
-        <v>92021</v>
+        <v>79726</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4926,30 +4911,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3100</v>
+        <v>6464</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4958,10 +4943,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730767</v>
+        <v>730825</v>
       </c>
       <c r="R41" t="n">
-        <v>7358759</v>
+        <v>7358734</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4994,6 +4979,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5020,10 +5010,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121590873</v>
+        <v>121590836</v>
       </c>
       <c r="B42" t="n">
-        <v>92012</v>
+        <v>79719</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5032,30 +5022,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2059</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5064,10 +5054,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730737</v>
+        <v>730893</v>
       </c>
       <c r="R42" t="n">
-        <v>7358829</v>
+        <v>7358778</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5100,6 +5090,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5126,10 +5121,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121590861</v>
+        <v>121590857</v>
       </c>
       <c r="B43" t="n">
-        <v>92024</v>
+        <v>79594</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5138,30 +5133,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5449</v>
+        <v>6456</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5170,10 +5165,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730810</v>
+        <v>730854</v>
       </c>
       <c r="R43" t="n">
-        <v>7358795</v>
+        <v>7358725</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5206,6 +5201,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5232,7 +5232,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121590847</v>
+        <v>121590877</v>
       </c>
       <c r="B44" t="n">
         <v>91990</v>
@@ -5267,7 +5267,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>730811</v>
+        <v>730725</v>
       </c>
       <c r="R44" t="n">
-        <v>7358748</v>
+        <v>7358827</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5338,7 +5338,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121590877</v>
+        <v>121590849</v>
       </c>
       <c r="B45" t="n">
         <v>91990</v>
@@ -5373,7 +5373,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>730725</v>
+        <v>730804</v>
       </c>
       <c r="R45" t="n">
-        <v>7358827</v>
+        <v>7358743</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5444,10 +5444,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121590840</v>
+        <v>121590835</v>
       </c>
       <c r="B46" t="n">
-        <v>97059</v>
+        <v>79726</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5460,21 +5460,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5488,10 +5488,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>731001</v>
+        <v>730890</v>
       </c>
       <c r="R46" t="n">
-        <v>7358693</v>
+        <v>7358797</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5524,6 +5524,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,10 +5555,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121590870</v>
+        <v>121590880</v>
       </c>
       <c r="B47" t="n">
-        <v>77541</v>
+        <v>91996</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5562,25 +5567,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5594,10 +5599,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730756</v>
+        <v>730731</v>
       </c>
       <c r="R47" t="n">
-        <v>7358818</v>
+        <v>7358821</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5630,11 +5635,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5661,10 +5661,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121590864</v>
+        <v>121590874</v>
       </c>
       <c r="B48" t="n">
-        <v>91996</v>
+        <v>91990</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5673,30 +5673,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730835</v>
+        <v>730724</v>
       </c>
       <c r="R48" t="n">
-        <v>7358839</v>
+        <v>7358840</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>

--- a/artfynd/A 71374-2021 artfynd.xlsx
+++ b/artfynd/A 71374-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121590869</v>
+        <v>121590854</v>
       </c>
       <c r="B2" t="n">
-        <v>77993</v>
+        <v>79691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730756</v>
+        <v>730828</v>
       </c>
       <c r="R2" t="n">
-        <v>7358818</v>
+        <v>7358733</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121590859</v>
+        <v>121590841</v>
       </c>
       <c r="B3" t="n">
-        <v>77541</v>
+        <v>82393</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730851</v>
+        <v>730998</v>
       </c>
       <c r="R3" t="n">
-        <v>7358729</v>
+        <v>7358696</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På grov gammal kolad tallhögstubbe</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121590879</v>
+        <v>121590873</v>
       </c>
       <c r="B4" t="n">
         <v>92012</v>
@@ -932,7 +932,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730730</v>
+        <v>730737</v>
       </c>
       <c r="R4" t="n">
-        <v>7358824</v>
+        <v>7358829</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1003,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121590840</v>
+        <v>121590853</v>
       </c>
       <c r="B5" t="n">
-        <v>97059</v>
+        <v>79726</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>731001</v>
+        <v>730825</v>
       </c>
       <c r="R5" t="n">
-        <v>7358693</v>
+        <v>7358734</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,6 +1083,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121590845</v>
+        <v>121590859</v>
       </c>
       <c r="B6" t="n">
-        <v>91988</v>
+        <v>77541</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,26 +1130,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>6487</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1153,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730764</v>
+        <v>730851</v>
       </c>
       <c r="R6" t="n">
-        <v>7358768</v>
+        <v>7358729</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1189,6 +1194,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På grov gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121590852</v>
+        <v>121590840</v>
       </c>
       <c r="B7" t="n">
-        <v>79719</v>
+        <v>97059</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1241,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1259,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730829</v>
+        <v>731001</v>
       </c>
       <c r="R7" t="n">
-        <v>7358728</v>
+        <v>7358693</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1295,11 +1305,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121590872</v>
+        <v>121590871</v>
       </c>
       <c r="B8" t="n">
-        <v>91990</v>
+        <v>79198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1342,26 +1347,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4362</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1370,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730741</v>
+        <v>730758</v>
       </c>
       <c r="R8" t="n">
-        <v>7358824</v>
+        <v>7358818</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1406,6 +1411,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121590854</v>
+        <v>121590861</v>
       </c>
       <c r="B9" t="n">
-        <v>79691</v>
+        <v>92024</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1448,26 +1458,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>5449</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1476,10 +1486,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730828</v>
+        <v>730810</v>
       </c>
       <c r="R9" t="n">
-        <v>7358733</v>
+        <v>7358795</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1512,11 +1522,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1543,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121590843</v>
+        <v>121590874</v>
       </c>
       <c r="B10" t="n">
-        <v>79719</v>
+        <v>91990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1555,30 +1560,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6462</v>
+        <v>4362</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1587,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730936</v>
+        <v>730724</v>
       </c>
       <c r="R10" t="n">
-        <v>7358694</v>
+        <v>7358840</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1623,11 +1628,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121590873</v>
+        <v>121590855</v>
       </c>
       <c r="B11" t="n">
-        <v>92012</v>
+        <v>79725</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1666,30 +1666,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2059</v>
+        <v>6463</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730737</v>
+        <v>730855</v>
       </c>
       <c r="R11" t="n">
-        <v>7358829</v>
+        <v>7358731</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1734,6 +1734,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1760,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121590871</v>
+        <v>121590843</v>
       </c>
       <c r="B12" t="n">
-        <v>79198</v>
+        <v>79719</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1772,25 +1777,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1804,10 +1809,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730758</v>
+        <v>730936</v>
       </c>
       <c r="R12" t="n">
-        <v>7358818</v>
+        <v>7358694</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1844,7 +1849,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121590844</v>
+        <v>121590847</v>
       </c>
       <c r="B13" t="n">
-        <v>79726</v>
+        <v>91990</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,30 +1888,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1915,10 +1920,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730907</v>
+        <v>730811</v>
       </c>
       <c r="R13" t="n">
-        <v>7358717</v>
+        <v>7358748</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1951,11 +1956,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121590881</v>
+        <v>121590882</v>
       </c>
       <c r="B14" t="n">
-        <v>89396</v>
+        <v>91990</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1994,30 +1994,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730733</v>
+        <v>730749</v>
       </c>
       <c r="R14" t="n">
-        <v>7358825</v>
+        <v>7358805</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121590855</v>
+        <v>121590876</v>
       </c>
       <c r="B15" t="n">
-        <v>79725</v>
+        <v>92008</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2104,21 +2104,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>4366</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730855</v>
+        <v>730724</v>
       </c>
       <c r="R15" t="n">
-        <v>7358731</v>
+        <v>7358834</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2168,11 +2168,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2199,10 +2194,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121590842</v>
+        <v>121590883</v>
       </c>
       <c r="B16" t="n">
-        <v>91282</v>
+        <v>92024</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2211,30 +2206,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>760</v>
+        <v>5449</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2243,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730938</v>
+        <v>730758</v>
       </c>
       <c r="R16" t="n">
-        <v>7358696</v>
+        <v>7358773</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2279,11 +2274,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2310,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121590863</v>
+        <v>121590856</v>
       </c>
       <c r="B17" t="n">
-        <v>97065</v>
+        <v>97059</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2326,16 +2316,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2354,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730859</v>
+        <v>730873</v>
       </c>
       <c r="R17" t="n">
-        <v>7358837</v>
+        <v>7358715</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2416,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121590837</v>
+        <v>121590852</v>
       </c>
       <c r="B18" t="n">
-        <v>90738</v>
+        <v>79719</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2428,25 +2418,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2460,10 +2450,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730955</v>
+        <v>730829</v>
       </c>
       <c r="R18" t="n">
-        <v>7358774</v>
+        <v>7358728</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2500,7 +2490,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På granhögstubbe och -låga</t>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2527,10 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121590839</v>
+        <v>121590851</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>91990</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2543,26 +2533,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2571,10 +2561,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>731001</v>
+        <v>730803</v>
       </c>
       <c r="R19" t="n">
-        <v>7358729</v>
+        <v>7358733</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2607,11 +2597,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Mindre ex på en gammal gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2638,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121590838</v>
+        <v>121590839</v>
       </c>
       <c r="B20" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2654,21 +2639,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2682,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730995</v>
+        <v>731001</v>
       </c>
       <c r="R20" t="n">
-        <v>7358751</v>
+        <v>7358729</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2718,6 +2703,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Mindre ex på en gammal gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2744,10 +2734,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121590851</v>
+        <v>121590868</v>
       </c>
       <c r="B21" t="n">
-        <v>91990</v>
+        <v>79227</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2760,26 +2750,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2788,10 +2778,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730803</v>
+        <v>730799</v>
       </c>
       <c r="R21" t="n">
-        <v>7358733</v>
+        <v>7358812</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2824,6 +2814,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2850,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121590876</v>
+        <v>121590877</v>
       </c>
       <c r="B22" t="n">
-        <v>92008</v>
+        <v>91990</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2862,30 +2857,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2894,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730724</v>
+        <v>730725</v>
       </c>
       <c r="R22" t="n">
-        <v>7358834</v>
+        <v>7358827</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3067,10 +3062,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121590870</v>
+        <v>121590850</v>
       </c>
       <c r="B24" t="n">
-        <v>77541</v>
+        <v>91996</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3079,30 +3074,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3111,10 +3106,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730756</v>
+        <v>730806</v>
       </c>
       <c r="R24" t="n">
-        <v>7358818</v>
+        <v>7358740</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3147,11 +3142,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3178,10 +3168,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121590834</v>
+        <v>121590849</v>
       </c>
       <c r="B25" t="n">
-        <v>57372</v>
+        <v>91990</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3194,26 +3184,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3222,10 +3212,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>731015</v>
+        <v>730804</v>
       </c>
       <c r="R25" t="n">
-        <v>7358724</v>
+        <v>7358743</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3258,11 +3248,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Födosökshack i tallöverståndare</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3289,10 +3274,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121590885</v>
+        <v>121590880</v>
       </c>
       <c r="B26" t="n">
-        <v>92008</v>
+        <v>91996</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3305,26 +3290,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3333,10 +3318,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730757</v>
+        <v>730731</v>
       </c>
       <c r="R26" t="n">
-        <v>7358754</v>
+        <v>7358821</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3395,10 +3380,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121590847</v>
+        <v>121590860</v>
       </c>
       <c r="B27" t="n">
-        <v>91990</v>
+        <v>78345</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3411,26 +3396,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3439,7 +3424,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730811</v>
+        <v>730824</v>
       </c>
       <c r="R27" t="n">
         <v>7358748</v>
@@ -3475,6 +3460,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På grov gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3501,10 +3491,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121590850</v>
+        <v>121590884</v>
       </c>
       <c r="B28" t="n">
-        <v>91996</v>
+        <v>92021</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3513,30 +3503,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3545,10 +3535,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730806</v>
+        <v>730767</v>
       </c>
       <c r="R28" t="n">
-        <v>7358740</v>
+        <v>7358759</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3607,10 +3597,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121590884</v>
+        <v>121590866</v>
       </c>
       <c r="B29" t="n">
-        <v>92021</v>
+        <v>78345</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3623,26 +3613,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3100</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3651,10 +3641,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730767</v>
+        <v>730818</v>
       </c>
       <c r="R29" t="n">
-        <v>7358759</v>
+        <v>7358836</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3687,6 +3677,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3713,10 +3708,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121590860</v>
+        <v>121590870</v>
       </c>
       <c r="B30" t="n">
-        <v>78345</v>
+        <v>77541</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3729,21 +3724,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3757,10 +3752,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730824</v>
+        <v>730756</v>
       </c>
       <c r="R30" t="n">
-        <v>7358748</v>
+        <v>7358818</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3797,7 +3792,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På grov gammal kolad tallstubbe</t>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3824,10 +3819,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121590841</v>
+        <v>121590857</v>
       </c>
       <c r="B31" t="n">
-        <v>82393</v>
+        <v>79594</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3836,25 +3831,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>6456</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3868,10 +3863,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730998</v>
+        <v>730854</v>
       </c>
       <c r="R31" t="n">
-        <v>7358696</v>
+        <v>7358725</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3908,7 +3903,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3935,10 +3930,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121590861</v>
+        <v>121590881</v>
       </c>
       <c r="B32" t="n">
-        <v>92024</v>
+        <v>89396</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3947,30 +3942,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3979,10 +3974,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730810</v>
+        <v>730733</v>
       </c>
       <c r="R32" t="n">
-        <v>7358795</v>
+        <v>7358825</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4041,10 +4036,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121590848</v>
+        <v>121590835</v>
       </c>
       <c r="B33" t="n">
-        <v>92021</v>
+        <v>79726</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4053,25 +4048,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3100</v>
+        <v>6464</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4085,10 +4080,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730804</v>
+        <v>730890</v>
       </c>
       <c r="R33" t="n">
-        <v>7358743</v>
+        <v>7358797</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4121,6 +4116,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4147,10 +4147,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121590866</v>
+        <v>121590863</v>
       </c>
       <c r="B34" t="n">
-        <v>78345</v>
+        <v>97065</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4159,25 +4159,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730818</v>
+        <v>730859</v>
       </c>
       <c r="R34" t="n">
-        <v>7358836</v>
+        <v>7358837</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4227,11 +4227,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4258,10 +4253,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121590856</v>
+        <v>121590885</v>
       </c>
       <c r="B35" t="n">
-        <v>97059</v>
+        <v>92008</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4274,26 +4269,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>4366</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4302,10 +4297,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730873</v>
+        <v>730757</v>
       </c>
       <c r="R35" t="n">
-        <v>7358715</v>
+        <v>7358754</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4364,10 +4359,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121590883</v>
+        <v>121590872</v>
       </c>
       <c r="B36" t="n">
-        <v>92024</v>
+        <v>91990</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4380,26 +4375,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4408,10 +4403,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730758</v>
+        <v>730741</v>
       </c>
       <c r="R36" t="n">
-        <v>7358773</v>
+        <v>7358824</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4470,10 +4465,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121590868</v>
+        <v>121590842</v>
       </c>
       <c r="B37" t="n">
-        <v>79227</v>
+        <v>91282</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4482,25 +4477,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>760</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4514,10 +4509,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730799</v>
+        <v>730938</v>
       </c>
       <c r="R37" t="n">
-        <v>7358812</v>
+        <v>7358696</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4554,7 +4549,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal kolad tallstubbe</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4581,10 +4576,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121590864</v>
+        <v>121590837</v>
       </c>
       <c r="B38" t="n">
-        <v>91996</v>
+        <v>90738</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4593,30 +4588,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4625,10 +4620,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730835</v>
+        <v>730955</v>
       </c>
       <c r="R38" t="n">
-        <v>7358839</v>
+        <v>7358774</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4661,6 +4656,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På granhögstubbe och -låga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4687,10 +4687,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121590882</v>
+        <v>121590836</v>
       </c>
       <c r="B39" t="n">
-        <v>91990</v>
+        <v>79719</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4699,30 +4699,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4731,10 +4731,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730749</v>
+        <v>730893</v>
       </c>
       <c r="R39" t="n">
-        <v>7358805</v>
+        <v>7358778</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4767,6 +4767,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4793,10 +4798,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121590846</v>
+        <v>121590838</v>
       </c>
       <c r="B40" t="n">
-        <v>92021</v>
+        <v>82393</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4809,26 +4814,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3100</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4837,10 +4842,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730810</v>
+        <v>730995</v>
       </c>
       <c r="R40" t="n">
-        <v>7358754</v>
+        <v>7358751</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4899,10 +4904,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121590853</v>
+        <v>121590879</v>
       </c>
       <c r="B41" t="n">
-        <v>79726</v>
+        <v>92012</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4911,30 +4916,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6464</v>
+        <v>2059</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4943,10 +4948,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730825</v>
+        <v>730730</v>
       </c>
       <c r="R41" t="n">
-        <v>7358734</v>
+        <v>7358824</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4979,11 +4984,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5010,10 +5010,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121590836</v>
+        <v>121590846</v>
       </c>
       <c r="B42" t="n">
-        <v>79719</v>
+        <v>92021</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5022,30 +5022,30 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>3100</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730893</v>
+        <v>730810</v>
       </c>
       <c r="R42" t="n">
-        <v>7358778</v>
+        <v>7358754</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5090,11 +5090,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5121,10 +5116,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121590857</v>
+        <v>121590869</v>
       </c>
       <c r="B43" t="n">
-        <v>79594</v>
+        <v>77993</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5133,25 +5128,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6456</v>
+        <v>6437</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5165,10 +5160,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730854</v>
+        <v>730756</v>
       </c>
       <c r="R43" t="n">
-        <v>7358725</v>
+        <v>7358818</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5205,7 +5200,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5232,10 +5227,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121590877</v>
+        <v>121590844</v>
       </c>
       <c r="B44" t="n">
-        <v>91990</v>
+        <v>79726</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5244,30 +5239,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4362</v>
+        <v>6464</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5276,10 +5271,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>730725</v>
+        <v>730907</v>
       </c>
       <c r="R44" t="n">
-        <v>7358827</v>
+        <v>7358717</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5312,6 +5307,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5338,10 +5338,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121590849</v>
+        <v>121590834</v>
       </c>
       <c r="B45" t="n">
-        <v>91990</v>
+        <v>57372</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5354,26 +5354,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4362</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>730804</v>
+        <v>731015</v>
       </c>
       <c r="R45" t="n">
-        <v>7358743</v>
+        <v>7358724</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5418,6 +5418,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Födosökshack i tallöverståndare</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5444,10 +5449,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121590835</v>
+        <v>121590848</v>
       </c>
       <c r="B46" t="n">
-        <v>79726</v>
+        <v>92021</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5456,25 +5461,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6464</v>
+        <v>3100</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5488,10 +5493,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>730890</v>
+        <v>730804</v>
       </c>
       <c r="R46" t="n">
-        <v>7358797</v>
+        <v>7358743</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5524,11 +5529,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5555,10 +5555,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121590880</v>
+        <v>121590845</v>
       </c>
       <c r="B47" t="n">
-        <v>91996</v>
+        <v>91988</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5567,30 +5567,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730731</v>
+        <v>730764</v>
       </c>
       <c r="R47" t="n">
-        <v>7358821</v>
+        <v>7358768</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5661,10 +5661,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121590874</v>
+        <v>121590864</v>
       </c>
       <c r="B48" t="n">
-        <v>91990</v>
+        <v>91996</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5673,30 +5673,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5705,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730724</v>
+        <v>730835</v>
       </c>
       <c r="R48" t="n">
-        <v>7358840</v>
+        <v>7358839</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>

--- a/artfynd/A 71374-2021 artfynd.xlsx
+++ b/artfynd/A 71374-2021 artfynd.xlsx
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121590859</v>
+        <v>121590840</v>
       </c>
       <c r="B6" t="n">
-        <v>77541</v>
+        <v>97059</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,25 +1126,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730851</v>
+        <v>731001</v>
       </c>
       <c r="R6" t="n">
-        <v>7358729</v>
+        <v>7358693</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1194,11 +1194,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På grov gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121590840</v>
+        <v>121590871</v>
       </c>
       <c r="B7" t="n">
-        <v>97059</v>
+        <v>79198</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,25 +1232,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1269,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>731001</v>
+        <v>730758</v>
       </c>
       <c r="R7" t="n">
-        <v>7358693</v>
+        <v>7358818</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1305,6 +1300,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121590871</v>
+        <v>121590859</v>
       </c>
       <c r="B8" t="n">
-        <v>79198</v>
+        <v>77541</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730758</v>
+        <v>730851</v>
       </c>
       <c r="R8" t="n">
-        <v>7358818</v>
+        <v>7358729</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
+          <t>På grov gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1876,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121590847</v>
+        <v>121590856</v>
       </c>
       <c r="B13" t="n">
-        <v>91990</v>
+        <v>97059</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1888,30 +1888,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4362</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1920,10 +1920,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730811</v>
+        <v>730873</v>
       </c>
       <c r="R13" t="n">
-        <v>7358748</v>
+        <v>7358715</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121590882</v>
+        <v>121590847</v>
       </c>
       <c r="B14" t="n">
         <v>91990</v>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730749</v>
+        <v>730811</v>
       </c>
       <c r="R14" t="n">
-        <v>7358805</v>
+        <v>7358748</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121590876</v>
+        <v>121590882</v>
       </c>
       <c r="B15" t="n">
-        <v>92008</v>
+        <v>91990</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2100,30 +2100,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730724</v>
+        <v>730749</v>
       </c>
       <c r="R15" t="n">
-        <v>7358834</v>
+        <v>7358805</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2194,10 +2194,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121590883</v>
+        <v>121590876</v>
       </c>
       <c r="B16" t="n">
-        <v>92024</v>
+        <v>92008</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2206,30 +2206,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2238,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730758</v>
+        <v>730724</v>
       </c>
       <c r="R16" t="n">
-        <v>7358773</v>
+        <v>7358834</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2300,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121590856</v>
+        <v>121590883</v>
       </c>
       <c r="B17" t="n">
-        <v>97059</v>
+        <v>92024</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2312,30 +2312,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>5449</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730873</v>
+        <v>730758</v>
       </c>
       <c r="R17" t="n">
-        <v>7358715</v>
+        <v>7358773</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2623,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121590839</v>
+        <v>121590868</v>
       </c>
       <c r="B20" t="n">
-        <v>78609</v>
+        <v>79227</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2639,21 +2639,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>731001</v>
+        <v>730799</v>
       </c>
       <c r="R20" t="n">
-        <v>7358729</v>
+        <v>7358812</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Mindre ex på en gammal gran</t>
+          <t>På gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2734,10 +2734,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121590868</v>
+        <v>121590839</v>
       </c>
       <c r="B21" t="n">
-        <v>79227</v>
+        <v>78609</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2750,21 +2750,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2778,10 +2778,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730799</v>
+        <v>731001</v>
       </c>
       <c r="R21" t="n">
-        <v>7358812</v>
+        <v>7358729</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gammal kolad tallstubbe</t>
+          <t>Mindre ex på en gammal gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3491,10 +3491,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121590884</v>
+        <v>121590870</v>
       </c>
       <c r="B28" t="n">
-        <v>92021</v>
+        <v>77541</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3507,26 +3507,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3100</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730767</v>
+        <v>730756</v>
       </c>
       <c r="R28" t="n">
-        <v>7358759</v>
+        <v>7358818</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3571,6 +3571,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3597,10 +3602,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121590866</v>
+        <v>121590884</v>
       </c>
       <c r="B29" t="n">
-        <v>78345</v>
+        <v>92021</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3613,26 +3618,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>3100</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3641,10 +3646,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730818</v>
+        <v>730767</v>
       </c>
       <c r="R29" t="n">
-        <v>7358836</v>
+        <v>7358759</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3677,11 +3682,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3708,10 +3708,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121590870</v>
+        <v>121590866</v>
       </c>
       <c r="B30" t="n">
-        <v>77541</v>
+        <v>78345</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3724,21 +3724,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730756</v>
+        <v>730818</v>
       </c>
       <c r="R30" t="n">
-        <v>7358818</v>
+        <v>7358836</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
+          <t>På gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5010,10 +5010,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121590846</v>
+        <v>121590869</v>
       </c>
       <c r="B42" t="n">
-        <v>92021</v>
+        <v>77993</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5026,26 +5026,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3100</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5054,10 +5054,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730810</v>
+        <v>730756</v>
       </c>
       <c r="R42" t="n">
-        <v>7358754</v>
+        <v>7358818</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5090,6 +5090,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5116,10 +5121,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121590869</v>
+        <v>121590846</v>
       </c>
       <c r="B43" t="n">
-        <v>77993</v>
+        <v>92021</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5132,26 +5137,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6437</v>
+        <v>3100</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5160,10 +5165,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730756</v>
+        <v>730810</v>
       </c>
       <c r="R43" t="n">
-        <v>7358818</v>
+        <v>7358754</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5196,11 +5201,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5338,10 +5338,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121590834</v>
+        <v>121590848</v>
       </c>
       <c r="B45" t="n">
-        <v>57372</v>
+        <v>92021</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5354,21 +5354,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>3100</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>731015</v>
+        <v>730804</v>
       </c>
       <c r="R45" t="n">
-        <v>7358724</v>
+        <v>7358743</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5418,11 +5418,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Födosökshack i tallöverståndare</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5449,10 +5444,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121590848</v>
+        <v>121590845</v>
       </c>
       <c r="B46" t="n">
-        <v>92021</v>
+        <v>91988</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5465,26 +5460,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5493,10 +5488,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>730804</v>
+        <v>730764</v>
       </c>
       <c r="R46" t="n">
-        <v>7358743</v>
+        <v>7358768</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5555,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121590845</v>
+        <v>121590864</v>
       </c>
       <c r="B47" t="n">
-        <v>91988</v>
+        <v>91996</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5567,30 +5562,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5599,10 +5594,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730764</v>
+        <v>730835</v>
       </c>
       <c r="R47" t="n">
-        <v>7358768</v>
+        <v>7358839</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5661,10 +5656,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121590864</v>
+        <v>121590834</v>
       </c>
       <c r="B48" t="n">
-        <v>91996</v>
+        <v>57372</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5673,30 +5668,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5705,10 +5700,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730835</v>
+        <v>731015</v>
       </c>
       <c r="R48" t="n">
-        <v>7358839</v>
+        <v>7358724</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5741,6 +5736,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Födosökshack i tallöverståndare</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 71374-2021 artfynd.xlsx
+++ b/artfynd/A 71374-2021 artfynd.xlsx
@@ -1114,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121590840</v>
+        <v>121590859</v>
       </c>
       <c r="B6" t="n">
-        <v>97059</v>
+        <v>77541</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,25 +1126,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6487</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>731001</v>
+        <v>730851</v>
       </c>
       <c r="R6" t="n">
-        <v>7358693</v>
+        <v>7358729</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1194,6 +1194,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På grov gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121590871</v>
+        <v>121590840</v>
       </c>
       <c r="B7" t="n">
-        <v>79198</v>
+        <v>97059</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1232,25 +1237,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1264,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730758</v>
+        <v>731001</v>
       </c>
       <c r="R7" t="n">
-        <v>7358818</v>
+        <v>7358693</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1300,11 +1305,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121590859</v>
+        <v>121590871</v>
       </c>
       <c r="B8" t="n">
-        <v>77541</v>
+        <v>79198</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1347,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730851</v>
+        <v>730758</v>
       </c>
       <c r="R8" t="n">
-        <v>7358729</v>
+        <v>7358818</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På grov gammal kolad tallhögstubbe</t>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -5338,10 +5338,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121590848</v>
+        <v>121590834</v>
       </c>
       <c r="B45" t="n">
-        <v>92021</v>
+        <v>57372</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5354,21 +5354,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3100</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5382,10 +5382,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>730804</v>
+        <v>731015</v>
       </c>
       <c r="R45" t="n">
-        <v>7358743</v>
+        <v>7358724</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5418,6 +5418,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Födosökshack i tallöverståndare</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5444,10 +5449,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121590845</v>
+        <v>121590848</v>
       </c>
       <c r="B46" t="n">
-        <v>91988</v>
+        <v>92021</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5460,26 +5465,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5488,10 +5493,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>730764</v>
+        <v>730804</v>
       </c>
       <c r="R46" t="n">
-        <v>7358768</v>
+        <v>7358743</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5550,10 +5555,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121590864</v>
+        <v>121590845</v>
       </c>
       <c r="B47" t="n">
-        <v>91996</v>
+        <v>91988</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5562,30 +5567,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5594,10 +5599,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730835</v>
+        <v>730764</v>
       </c>
       <c r="R47" t="n">
-        <v>7358839</v>
+        <v>7358768</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5656,10 +5661,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121590834</v>
+        <v>121590864</v>
       </c>
       <c r="B48" t="n">
-        <v>57372</v>
+        <v>91996</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5668,30 +5673,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5700,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>731015</v>
+        <v>730835</v>
       </c>
       <c r="R48" t="n">
-        <v>7358724</v>
+        <v>7358839</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5736,11 +5741,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Födosökshack i tallöverståndare</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 71374-2021 artfynd.xlsx
+++ b/artfynd/A 71374-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121590854</v>
+        <v>121590864</v>
       </c>
       <c r="B2" t="n">
-        <v>79691</v>
+        <v>92004</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730828</v>
+        <v>730835</v>
       </c>
       <c r="R2" t="n">
-        <v>7358733</v>
+        <v>7358839</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121590841</v>
+        <v>121590847</v>
       </c>
       <c r="B3" t="n">
-        <v>82393</v>
+        <v>91998</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,26 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730998</v>
+        <v>730811</v>
       </c>
       <c r="R3" t="n">
-        <v>7358696</v>
+        <v>7358748</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,11 +861,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121590873</v>
+        <v>121590849</v>
       </c>
       <c r="B4" t="n">
-        <v>92012</v>
+        <v>91998</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,26 +903,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730737</v>
+        <v>730804</v>
       </c>
       <c r="R4" t="n">
-        <v>7358829</v>
+        <v>7358743</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1003,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121590853</v>
+        <v>121590840</v>
       </c>
       <c r="B5" t="n">
-        <v>79726</v>
+        <v>97067</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730825</v>
+        <v>731001</v>
       </c>
       <c r="R5" t="n">
-        <v>7358734</v>
+        <v>7358693</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,11 +1073,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121590859</v>
+        <v>121590870</v>
       </c>
       <c r="B6" t="n">
-        <v>77541</v>
+        <v>77548</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730851</v>
+        <v>730756</v>
       </c>
       <c r="R6" t="n">
-        <v>7358729</v>
+        <v>7358818</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1198,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På grov gammal kolad tallhögstubbe</t>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121590840</v>
+        <v>121590844</v>
       </c>
       <c r="B7" t="n">
-        <v>97059</v>
+        <v>79733</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1241,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1269,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>731001</v>
+        <v>730907</v>
       </c>
       <c r="R7" t="n">
-        <v>7358693</v>
+        <v>7358717</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1305,6 +1290,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1331,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121590871</v>
+        <v>121590856</v>
       </c>
       <c r="B8" t="n">
-        <v>79198</v>
+        <v>97067</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1343,25 +1333,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1375,10 +1365,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730758</v>
+        <v>730873</v>
       </c>
       <c r="R8" t="n">
-        <v>7358818</v>
+        <v>7358715</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1411,11 +1401,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,10 +1427,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121590861</v>
+        <v>121590841</v>
       </c>
       <c r="B9" t="n">
-        <v>92024</v>
+        <v>82400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,26 +1443,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5449</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1486,10 +1471,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730810</v>
+        <v>730998</v>
       </c>
       <c r="R9" t="n">
-        <v>7358795</v>
+        <v>7358696</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1522,6 +1507,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1548,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121590874</v>
+        <v>121590869</v>
       </c>
       <c r="B10" t="n">
-        <v>91990</v>
+        <v>78000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,26 +1554,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1592,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730724</v>
+        <v>730756</v>
       </c>
       <c r="R10" t="n">
-        <v>7358840</v>
+        <v>7358818</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1628,6 +1618,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,10 +1649,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121590855</v>
+        <v>121590863</v>
       </c>
       <c r="B11" t="n">
-        <v>79725</v>
+        <v>97073</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1670,21 +1665,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>221941</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1698,10 +1693,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730855</v>
+        <v>730859</v>
       </c>
       <c r="R11" t="n">
-        <v>7358731</v>
+        <v>7358837</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1734,11 +1729,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121590843</v>
+        <v>121590874</v>
       </c>
       <c r="B12" t="n">
-        <v>79719</v>
+        <v>91998</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1777,30 +1767,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1809,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730936</v>
+        <v>730724</v>
       </c>
       <c r="R12" t="n">
-        <v>7358694</v>
+        <v>7358840</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1845,11 +1835,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121590856</v>
+        <v>121590880</v>
       </c>
       <c r="B13" t="n">
-        <v>97059</v>
+        <v>92004</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1892,21 +1877,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1920,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730873</v>
+        <v>730731</v>
       </c>
       <c r="R13" t="n">
-        <v>7358715</v>
+        <v>7358821</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1982,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121590847</v>
+        <v>121590866</v>
       </c>
       <c r="B14" t="n">
-        <v>91990</v>
+        <v>78352</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1998,26 +1983,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2026,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730811</v>
+        <v>730818</v>
       </c>
       <c r="R14" t="n">
-        <v>7358748</v>
+        <v>7358836</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2062,6 +2047,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121590882</v>
+        <v>121590853</v>
       </c>
       <c r="B15" t="n">
-        <v>91990</v>
+        <v>79733</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2100,30 +2090,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2132,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730749</v>
+        <v>730825</v>
       </c>
       <c r="R15" t="n">
-        <v>7358805</v>
+        <v>7358734</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2168,6 +2158,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2194,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121590876</v>
+        <v>121590838</v>
       </c>
       <c r="B16" t="n">
-        <v>92008</v>
+        <v>82400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2206,25 +2201,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4366</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2238,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730724</v>
+        <v>730995</v>
       </c>
       <c r="R16" t="n">
-        <v>7358834</v>
+        <v>7358751</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2300,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121590883</v>
+        <v>121590848</v>
       </c>
       <c r="B17" t="n">
-        <v>92024</v>
+        <v>92029</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2316,26 +2311,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5449</v>
+        <v>3100</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2344,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730758</v>
+        <v>730804</v>
       </c>
       <c r="R17" t="n">
-        <v>7358773</v>
+        <v>7358743</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2406,10 +2401,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121590852</v>
+        <v>121590861</v>
       </c>
       <c r="B18" t="n">
-        <v>79719</v>
+        <v>92032</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2418,30 +2413,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>5449</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2450,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730829</v>
+        <v>730810</v>
       </c>
       <c r="R18" t="n">
-        <v>7358728</v>
+        <v>7358795</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2486,11 +2481,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,10 +2507,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121590851</v>
+        <v>121590836</v>
       </c>
       <c r="B19" t="n">
-        <v>91990</v>
+        <v>79726</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2529,30 +2519,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2561,10 +2551,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730803</v>
+        <v>730893</v>
       </c>
       <c r="R19" t="n">
-        <v>7358733</v>
+        <v>7358778</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2597,6 +2587,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2623,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121590868</v>
+        <v>121590871</v>
       </c>
       <c r="B20" t="n">
-        <v>79227</v>
+        <v>79205</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2639,21 +2634,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2667,10 +2662,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730799</v>
+        <v>730758</v>
       </c>
       <c r="R20" t="n">
-        <v>7358812</v>
+        <v>7358818</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2707,7 +2702,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gammal kolad tallstubbe</t>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2734,10 +2729,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121590839</v>
+        <v>121590885</v>
       </c>
       <c r="B21" t="n">
-        <v>78609</v>
+        <v>92016</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2746,30 +2741,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>4366</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2778,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>731001</v>
+        <v>730757</v>
       </c>
       <c r="R21" t="n">
-        <v>7358729</v>
+        <v>7358754</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2814,11 +2809,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Mindre ex på en gammal gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2845,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121590877</v>
+        <v>121590859</v>
       </c>
       <c r="B22" t="n">
-        <v>91990</v>
+        <v>77548</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2861,26 +2851,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2889,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730725</v>
+        <v>730851</v>
       </c>
       <c r="R22" t="n">
-        <v>7358827</v>
+        <v>7358729</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2925,6 +2915,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På grov gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,10 +2946,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121590858</v>
+        <v>121590879</v>
       </c>
       <c r="B23" t="n">
-        <v>79719</v>
+        <v>92020</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2963,30 +2958,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>2059</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2995,10 +2990,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730856</v>
+        <v>730730</v>
       </c>
       <c r="R23" t="n">
-        <v>7358724</v>
+        <v>7358824</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3031,11 +3026,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3062,10 +3052,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121590850</v>
+        <v>121590857</v>
       </c>
       <c r="B24" t="n">
-        <v>91996</v>
+        <v>79601</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3078,26 +3068,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3106,10 +3096,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730806</v>
+        <v>730854</v>
       </c>
       <c r="R24" t="n">
-        <v>7358740</v>
+        <v>7358725</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3142,6 +3132,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3168,10 +3163,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121590849</v>
+        <v>121590860</v>
       </c>
       <c r="B25" t="n">
-        <v>91990</v>
+        <v>78352</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3184,26 +3179,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3212,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730804</v>
+        <v>730824</v>
       </c>
       <c r="R25" t="n">
-        <v>7358743</v>
+        <v>7358748</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3248,6 +3243,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På grov gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3274,10 +3274,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121590880</v>
+        <v>121590882</v>
       </c>
       <c r="B26" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3286,30 +3286,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730731</v>
+        <v>730749</v>
       </c>
       <c r="R26" t="n">
-        <v>7358821</v>
+        <v>7358805</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3380,10 +3380,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121590860</v>
+        <v>121590834</v>
       </c>
       <c r="B27" t="n">
-        <v>78345</v>
+        <v>57373</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3396,21 +3396,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730824</v>
+        <v>731015</v>
       </c>
       <c r="R27" t="n">
-        <v>7358748</v>
+        <v>7358724</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På grov gammal kolad tallstubbe</t>
+          <t>Födosökshack i tallöverståndare</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3491,10 +3491,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121590870</v>
+        <v>121590884</v>
       </c>
       <c r="B28" t="n">
-        <v>77541</v>
+        <v>92029</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3507,26 +3507,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>3100</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3535,10 +3535,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730756</v>
+        <v>730767</v>
       </c>
       <c r="R28" t="n">
-        <v>7358818</v>
+        <v>7358759</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3571,11 +3571,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3602,10 +3597,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121590884</v>
+        <v>121590839</v>
       </c>
       <c r="B29" t="n">
-        <v>92021</v>
+        <v>78616</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3618,26 +3613,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3100</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3646,10 +3641,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730767</v>
+        <v>731001</v>
       </c>
       <c r="R29" t="n">
-        <v>7358759</v>
+        <v>7358729</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3682,6 +3677,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Mindre ex på en gammal gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3708,10 +3708,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121590866</v>
+        <v>121590858</v>
       </c>
       <c r="B30" t="n">
-        <v>78345</v>
+        <v>79726</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3720,25 +3720,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730818</v>
+        <v>730856</v>
       </c>
       <c r="R30" t="n">
-        <v>7358836</v>
+        <v>7358724</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal kolad tallhögstubbe</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3819,10 +3819,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121590857</v>
+        <v>121590852</v>
       </c>
       <c r="B31" t="n">
-        <v>79594</v>
+        <v>79726</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3835,21 +3835,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6456</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3863,10 +3863,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730854</v>
+        <v>730829</v>
       </c>
       <c r="R31" t="n">
-        <v>7358725</v>
+        <v>7358728</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3930,10 +3930,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121590881</v>
+        <v>121590835</v>
       </c>
       <c r="B32" t="n">
-        <v>89396</v>
+        <v>79733</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3942,25 +3942,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6276</v>
+        <v>6464</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3974,10 +3974,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730733</v>
+        <v>730890</v>
       </c>
       <c r="R32" t="n">
-        <v>7358825</v>
+        <v>7358797</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4010,6 +4010,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,10 +4041,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121590835</v>
+        <v>121590872</v>
       </c>
       <c r="B33" t="n">
-        <v>79726</v>
+        <v>91998</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4048,30 +4053,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6464</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4080,10 +4085,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730890</v>
+        <v>730741</v>
       </c>
       <c r="R33" t="n">
-        <v>7358797</v>
+        <v>7358824</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4116,11 +4121,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4147,10 +4147,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121590863</v>
+        <v>121590843</v>
       </c>
       <c r="B34" t="n">
-        <v>97065</v>
+        <v>79726</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4163,21 +4163,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>6462</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730859</v>
+        <v>730936</v>
       </c>
       <c r="R34" t="n">
-        <v>7358837</v>
+        <v>7358694</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4227,6 +4227,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4253,10 +4258,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121590885</v>
+        <v>121590842</v>
       </c>
       <c r="B35" t="n">
-        <v>92008</v>
+        <v>91290</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4265,30 +4270,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4366</v>
+        <v>760</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4297,10 +4302,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730757</v>
+        <v>730938</v>
       </c>
       <c r="R35" t="n">
-        <v>7358754</v>
+        <v>7358696</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4333,6 +4338,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4359,10 +4369,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121590872</v>
+        <v>121590850</v>
       </c>
       <c r="B36" t="n">
-        <v>91990</v>
+        <v>92004</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4371,30 +4381,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4403,10 +4413,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730741</v>
+        <v>730806</v>
       </c>
       <c r="R36" t="n">
-        <v>7358824</v>
+        <v>7358740</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4465,10 +4475,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121590842</v>
+        <v>121590855</v>
       </c>
       <c r="B37" t="n">
-        <v>91282</v>
+        <v>79732</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4477,25 +4487,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>760</v>
+        <v>6463</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4509,10 +4519,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730938</v>
+        <v>730855</v>
       </c>
       <c r="R37" t="n">
-        <v>7358696</v>
+        <v>7358731</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4549,7 +4559,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4576,10 +4586,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121590837</v>
+        <v>121590876</v>
       </c>
       <c r="B38" t="n">
-        <v>90738</v>
+        <v>92016</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4588,25 +4598,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>4366</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4620,10 +4630,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730955</v>
+        <v>730724</v>
       </c>
       <c r="R38" t="n">
-        <v>7358774</v>
+        <v>7358834</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4656,11 +4666,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På granhögstubbe och -låga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4687,10 +4692,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121590836</v>
+        <v>121590845</v>
       </c>
       <c r="B39" t="n">
-        <v>79719</v>
+        <v>91996</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4699,30 +4704,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6462</v>
+        <v>4361</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4731,10 +4736,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730893</v>
+        <v>730764</v>
       </c>
       <c r="R39" t="n">
-        <v>7358778</v>
+        <v>7358768</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4767,11 +4772,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4798,10 +4798,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121590838</v>
+        <v>121590854</v>
       </c>
       <c r="B40" t="n">
-        <v>82393</v>
+        <v>79698</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4814,21 +4814,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730995</v>
+        <v>730828</v>
       </c>
       <c r="R40" t="n">
-        <v>7358751</v>
+        <v>7358733</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4878,6 +4878,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4904,10 +4909,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121590879</v>
+        <v>121590883</v>
       </c>
       <c r="B41" t="n">
-        <v>92012</v>
+        <v>92032</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4920,26 +4925,26 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2059</v>
+        <v>5449</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4948,10 +4953,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730730</v>
+        <v>730758</v>
       </c>
       <c r="R41" t="n">
-        <v>7358824</v>
+        <v>7358773</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5010,10 +5015,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121590869</v>
+        <v>121590846</v>
       </c>
       <c r="B42" t="n">
-        <v>77993</v>
+        <v>92029</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5026,26 +5031,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6437</v>
+        <v>3100</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5054,10 +5059,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730756</v>
+        <v>730810</v>
       </c>
       <c r="R42" t="n">
-        <v>7358818</v>
+        <v>7358754</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5090,11 +5095,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5121,10 +5121,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121590846</v>
+        <v>121590873</v>
       </c>
       <c r="B43" t="n">
-        <v>92021</v>
+        <v>92020</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5137,21 +5137,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730810</v>
+        <v>730737</v>
       </c>
       <c r="R43" t="n">
-        <v>7358754</v>
+        <v>7358829</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5227,10 +5227,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121590844</v>
+        <v>121590851</v>
       </c>
       <c r="B44" t="n">
-        <v>79726</v>
+        <v>91998</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5239,30 +5239,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6464</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>730907</v>
+        <v>730803</v>
       </c>
       <c r="R44" t="n">
-        <v>7358717</v>
+        <v>7358733</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5307,11 +5307,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5338,10 +5333,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121590834</v>
+        <v>121590837</v>
       </c>
       <c r="B45" t="n">
-        <v>57372</v>
+        <v>90746</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5354,21 +5349,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5382,10 +5377,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>731015</v>
+        <v>730955</v>
       </c>
       <c r="R45" t="n">
-        <v>7358724</v>
+        <v>7358774</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5422,7 +5417,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Födosökshack i tallöverståndare</t>
+          <t>På granhögstubbe och -låga</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5449,10 +5444,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121590848</v>
+        <v>121590881</v>
       </c>
       <c r="B46" t="n">
-        <v>92021</v>
+        <v>89403</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5461,25 +5456,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3100</v>
+        <v>6276</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5493,10 +5488,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>730804</v>
+        <v>730733</v>
       </c>
       <c r="R46" t="n">
-        <v>7358743</v>
+        <v>7358825</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5555,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121590845</v>
+        <v>121590877</v>
       </c>
       <c r="B47" t="n">
-        <v>91988</v>
+        <v>91998</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5571,26 +5566,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5599,10 +5594,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730764</v>
+        <v>730725</v>
       </c>
       <c r="R47" t="n">
-        <v>7358768</v>
+        <v>7358827</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5661,10 +5656,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121590864</v>
+        <v>121590868</v>
       </c>
       <c r="B48" t="n">
-        <v>91996</v>
+        <v>79234</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5673,30 +5668,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -5705,10 +5700,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730835</v>
+        <v>730799</v>
       </c>
       <c r="R48" t="n">
-        <v>7358839</v>
+        <v>7358812</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5741,6 +5736,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 71374-2021 artfynd.xlsx
+++ b/artfynd/A 71374-2021 artfynd.xlsx
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121590866</v>
+        <v>121590853</v>
       </c>
       <c r="B14" t="n">
-        <v>78352</v>
+        <v>79733</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,25 +1979,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730818</v>
+        <v>730825</v>
       </c>
       <c r="R14" t="n">
-        <v>7358836</v>
+        <v>7358734</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal kolad tallhögstubbe</t>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2078,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121590853</v>
+        <v>121590866</v>
       </c>
       <c r="B15" t="n">
-        <v>79733</v>
+        <v>78352</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,25 +2090,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6464</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730825</v>
+        <v>730818</v>
       </c>
       <c r="R15" t="n">
-        <v>7358734</v>
+        <v>7358836</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På grov sälg</t>
+          <t>På gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -4475,10 +4475,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121590855</v>
+        <v>121590876</v>
       </c>
       <c r="B37" t="n">
-        <v>79732</v>
+        <v>92016</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4491,21 +4491,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6463</v>
+        <v>4366</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4519,10 +4519,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730855</v>
+        <v>730724</v>
       </c>
       <c r="R37" t="n">
-        <v>7358731</v>
+        <v>7358834</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4555,11 +4555,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4586,10 +4581,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121590876</v>
+        <v>121590845</v>
       </c>
       <c r="B38" t="n">
-        <v>92016</v>
+        <v>91996</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4598,30 +4593,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4630,10 +4625,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730724</v>
+        <v>730764</v>
       </c>
       <c r="R38" t="n">
-        <v>7358834</v>
+        <v>7358768</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4692,10 +4687,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121590845</v>
+        <v>121590854</v>
       </c>
       <c r="B39" t="n">
-        <v>91996</v>
+        <v>79698</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4708,26 +4703,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4361</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4736,10 +4731,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730764</v>
+        <v>730828</v>
       </c>
       <c r="R39" t="n">
-        <v>7358768</v>
+        <v>7358733</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4772,6 +4767,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4798,10 +4798,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121590854</v>
+        <v>121590883</v>
       </c>
       <c r="B40" t="n">
-        <v>79698</v>
+        <v>92032</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4814,26 +4814,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2081</v>
+        <v>5449</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4842,10 +4842,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730828</v>
+        <v>730758</v>
       </c>
       <c r="R40" t="n">
-        <v>7358733</v>
+        <v>7358773</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4878,11 +4878,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4909,10 +4904,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121590883</v>
+        <v>121590855</v>
       </c>
       <c r="B41" t="n">
-        <v>92032</v>
+        <v>79732</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4921,30 +4916,30 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5449</v>
+        <v>6463</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4953,10 +4948,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730758</v>
+        <v>730855</v>
       </c>
       <c r="R41" t="n">
-        <v>7358773</v>
+        <v>7358731</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4989,6 +4984,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5015,10 +5015,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121590846</v>
+        <v>121590873</v>
       </c>
       <c r="B42" t="n">
-        <v>92029</v>
+        <v>92020</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5031,21 +5031,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3100</v>
+        <v>2059</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5059,10 +5059,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730810</v>
+        <v>730737</v>
       </c>
       <c r="R42" t="n">
-        <v>7358754</v>
+        <v>7358829</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5121,10 +5121,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121590873</v>
+        <v>121590846</v>
       </c>
       <c r="B43" t="n">
-        <v>92020</v>
+        <v>92029</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5137,21 +5137,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2059</v>
+        <v>3100</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5165,10 +5165,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730737</v>
+        <v>730810</v>
       </c>
       <c r="R43" t="n">
-        <v>7358829</v>
+        <v>7358754</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>

--- a/artfynd/A 71374-2021 artfynd.xlsx
+++ b/artfynd/A 71374-2021 artfynd.xlsx
@@ -2189,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121590838</v>
+        <v>121590836</v>
       </c>
       <c r="B16" t="n">
-        <v>82400</v>
+        <v>79726</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2201,25 +2201,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>6462</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730995</v>
+        <v>730893</v>
       </c>
       <c r="R16" t="n">
-        <v>7358751</v>
+        <v>7358778</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2269,6 +2269,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121590848</v>
+        <v>121590871</v>
       </c>
       <c r="B17" t="n">
-        <v>92029</v>
+        <v>79205</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2311,21 +2316,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3100</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2339,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730804</v>
+        <v>730758</v>
       </c>
       <c r="R17" t="n">
-        <v>7358743</v>
+        <v>7358818</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2375,6 +2380,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2401,10 +2411,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121590861</v>
+        <v>121590838</v>
       </c>
       <c r="B18" t="n">
-        <v>92032</v>
+        <v>82400</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2417,26 +2427,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5449</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2445,10 +2455,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730810</v>
+        <v>730995</v>
       </c>
       <c r="R18" t="n">
-        <v>7358795</v>
+        <v>7358751</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2507,10 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121590836</v>
+        <v>121590848</v>
       </c>
       <c r="B19" t="n">
-        <v>79726</v>
+        <v>92029</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2519,25 +2529,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>3100</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2551,10 +2561,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730893</v>
+        <v>730804</v>
       </c>
       <c r="R19" t="n">
-        <v>7358778</v>
+        <v>7358743</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2587,11 +2597,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2618,10 +2623,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121590871</v>
+        <v>121590861</v>
       </c>
       <c r="B20" t="n">
-        <v>79205</v>
+        <v>92032</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2634,26 +2639,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229821</v>
+        <v>5449</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2662,10 +2667,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730758</v>
+        <v>730810</v>
       </c>
       <c r="R20" t="n">
-        <v>7358818</v>
+        <v>7358795</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2698,11 +2703,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 71374-2021 artfynd.xlsx
+++ b/artfynd/A 71374-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121590870</v>
+        <v>121590881</v>
       </c>
       <c r="B2" t="n">
-        <v>77548</v>
+        <v>89403</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6487</v>
+        <v>6276</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730756</v>
+        <v>730733</v>
       </c>
       <c r="R2" t="n">
-        <v>7358818</v>
+        <v>7358825</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121590853</v>
+        <v>121590836</v>
       </c>
       <c r="B3" t="n">
-        <v>79733</v>
+        <v>79726</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730825</v>
+        <v>730893</v>
       </c>
       <c r="R3" t="n">
-        <v>7358734</v>
+        <v>7358778</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +865,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På grov sälg</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121590844</v>
+        <v>121590877</v>
       </c>
       <c r="B4" t="n">
-        <v>79733</v>
+        <v>91998</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,30 +904,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -941,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730907</v>
+        <v>730725</v>
       </c>
       <c r="R4" t="n">
-        <v>7358717</v>
+        <v>7358827</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -977,11 +972,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121590847</v>
+        <v>121590858</v>
       </c>
       <c r="B5" t="n">
-        <v>91998</v>
+        <v>79726</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,30 +1010,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1052,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730811</v>
+        <v>730856</v>
       </c>
       <c r="R5" t="n">
-        <v>7358748</v>
+        <v>7358724</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,6 +1078,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121590861</v>
+        <v>121590850</v>
       </c>
       <c r="B6" t="n">
-        <v>92032</v>
+        <v>92004</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1126,30 +1121,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1158,10 +1153,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730810</v>
+        <v>730806</v>
       </c>
       <c r="R6" t="n">
-        <v>7358795</v>
+        <v>7358740</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121590856</v>
+        <v>121590853</v>
       </c>
       <c r="B7" t="n">
-        <v>97067</v>
+        <v>79733</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1264,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730873</v>
+        <v>730825</v>
       </c>
       <c r="R7" t="n">
-        <v>7358715</v>
+        <v>7358734</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1300,6 +1295,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,10 +1326,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121590850</v>
+        <v>121590849</v>
       </c>
       <c r="B8" t="n">
-        <v>92004</v>
+        <v>91998</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1338,30 +1338,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730806</v>
+        <v>730804</v>
       </c>
       <c r="R8" t="n">
-        <v>7358740</v>
+        <v>7358743</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121590877</v>
+        <v>121590851</v>
       </c>
       <c r="B9" t="n">
         <v>91998</v>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730725</v>
+        <v>730803</v>
       </c>
       <c r="R9" t="n">
-        <v>7358827</v>
+        <v>7358733</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121590841</v>
+        <v>121590848</v>
       </c>
       <c r="B10" t="n">
-        <v>82400</v>
+        <v>92029</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,21 +1554,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>3100</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730998</v>
+        <v>730804</v>
       </c>
       <c r="R10" t="n">
-        <v>7358696</v>
+        <v>7358743</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1618,11 +1618,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,10 +1644,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121590864</v>
+        <v>121590856</v>
       </c>
       <c r="B11" t="n">
-        <v>92004</v>
+        <v>97067</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1665,26 +1660,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1693,10 +1688,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730835</v>
+        <v>730873</v>
       </c>
       <c r="R11" t="n">
-        <v>7358839</v>
+        <v>7358715</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1755,10 +1750,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121590854</v>
+        <v>121590868</v>
       </c>
       <c r="B12" t="n">
-        <v>79698</v>
+        <v>79234</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,21 +1766,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1799,10 +1794,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730828</v>
+        <v>730799</v>
       </c>
       <c r="R12" t="n">
-        <v>7358733</v>
+        <v>7358812</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1839,7 +1834,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På grov sälg</t>
+          <t>På gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1866,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121590838</v>
+        <v>121590859</v>
       </c>
       <c r="B13" t="n">
-        <v>82400</v>
+        <v>77548</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1882,21 +1877,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1910,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730995</v>
+        <v>730851</v>
       </c>
       <c r="R13" t="n">
-        <v>7358751</v>
+        <v>7358729</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1946,6 +1941,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På grov gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,10 +1972,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121590860</v>
+        <v>121590883</v>
       </c>
       <c r="B14" t="n">
-        <v>78352</v>
+        <v>92032</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1988,26 +1988,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730824</v>
+        <v>730758</v>
       </c>
       <c r="R14" t="n">
-        <v>7358748</v>
+        <v>7358773</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2052,11 +2052,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På grov gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2083,10 +2078,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121590837</v>
+        <v>121590854</v>
       </c>
       <c r="B15" t="n">
-        <v>90746</v>
+        <v>79698</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2099,21 +2094,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2127,10 +2122,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730955</v>
+        <v>730828</v>
       </c>
       <c r="R15" t="n">
-        <v>7358774</v>
+        <v>7358733</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2167,7 +2162,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På granhögstubbe och -låga</t>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2194,10 +2189,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121590880</v>
+        <v>121590847</v>
       </c>
       <c r="B16" t="n">
-        <v>92004</v>
+        <v>91998</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2206,30 +2201,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2238,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730731</v>
+        <v>730811</v>
       </c>
       <c r="R16" t="n">
-        <v>7358821</v>
+        <v>7358748</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2300,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121590851</v>
+        <v>121590841</v>
       </c>
       <c r="B17" t="n">
-        <v>91998</v>
+        <v>82400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2316,26 +2311,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4362</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2344,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730803</v>
+        <v>730998</v>
       </c>
       <c r="R17" t="n">
-        <v>7358733</v>
+        <v>7358696</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2380,6 +2375,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121590858</v>
+        <v>121590864</v>
       </c>
       <c r="B18" t="n">
-        <v>79726</v>
+        <v>92004</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2422,26 +2422,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730856</v>
+        <v>730835</v>
       </c>
       <c r="R18" t="n">
-        <v>7358724</v>
+        <v>7358839</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2486,11 +2486,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,10 +2512,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121590855</v>
+        <v>121590874</v>
       </c>
       <c r="B19" t="n">
-        <v>79732</v>
+        <v>91998</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2529,30 +2524,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>4362</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2561,10 +2556,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730855</v>
+        <v>730724</v>
       </c>
       <c r="R19" t="n">
-        <v>7358731</v>
+        <v>7358840</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2597,11 +2592,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2628,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121590882</v>
+        <v>121590846</v>
       </c>
       <c r="B20" t="n">
-        <v>91998</v>
+        <v>92029</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2644,26 +2634,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2672,10 +2662,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730749</v>
+        <v>730810</v>
       </c>
       <c r="R20" t="n">
-        <v>7358805</v>
+        <v>7358754</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2734,10 +2724,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121590873</v>
+        <v>121590842</v>
       </c>
       <c r="B21" t="n">
-        <v>92020</v>
+        <v>91290</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2746,30 +2736,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>760</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2778,10 +2768,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730737</v>
+        <v>730938</v>
       </c>
       <c r="R21" t="n">
-        <v>7358829</v>
+        <v>7358696</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2814,6 +2804,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2840,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121590868</v>
+        <v>121590844</v>
       </c>
       <c r="B22" t="n">
-        <v>79234</v>
+        <v>79733</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2852,25 +2847,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -2884,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730799</v>
+        <v>730907</v>
       </c>
       <c r="R22" t="n">
-        <v>7358812</v>
+        <v>7358717</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2924,7 +2919,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal kolad tallstubbe</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,10 +2946,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121590876</v>
+        <v>121590835</v>
       </c>
       <c r="B23" t="n">
-        <v>92016</v>
+        <v>79733</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2967,21 +2962,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4366</v>
+        <v>6464</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2995,10 +2990,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730724</v>
+        <v>730890</v>
       </c>
       <c r="R23" t="n">
-        <v>7358834</v>
+        <v>7358797</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3031,6 +3026,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3057,10 +3057,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121590879</v>
+        <v>121590885</v>
       </c>
       <c r="B24" t="n">
-        <v>92020</v>
+        <v>92016</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3069,30 +3069,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730730</v>
+        <v>730757</v>
       </c>
       <c r="R24" t="n">
-        <v>7358824</v>
+        <v>7358754</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3163,10 +3163,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121590885</v>
+        <v>121590840</v>
       </c>
       <c r="B25" t="n">
-        <v>92016</v>
+        <v>97067</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3179,26 +3179,26 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730757</v>
+        <v>731001</v>
       </c>
       <c r="R25" t="n">
-        <v>7358754</v>
+        <v>7358693</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3269,10 +3269,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121590845</v>
+        <v>121590884</v>
       </c>
       <c r="B26" t="n">
-        <v>91996</v>
+        <v>92029</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3285,26 +3285,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>3100</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730764</v>
+        <v>730767</v>
       </c>
       <c r="R26" t="n">
-        <v>7358768</v>
+        <v>7358759</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3375,10 +3375,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121590843</v>
+        <v>121590872</v>
       </c>
       <c r="B27" t="n">
-        <v>79726</v>
+        <v>91998</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3387,30 +3387,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6462</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730936</v>
+        <v>730741</v>
       </c>
       <c r="R27" t="n">
-        <v>7358694</v>
+        <v>7358824</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3455,11 +3455,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3486,10 +3481,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121590874</v>
+        <v>121590866</v>
       </c>
       <c r="B28" t="n">
-        <v>91998</v>
+        <v>78352</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3502,26 +3497,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3530,10 +3525,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730724</v>
+        <v>730818</v>
       </c>
       <c r="R28" t="n">
-        <v>7358840</v>
+        <v>7358836</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3566,6 +3561,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3592,10 +3592,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121590852</v>
+        <v>121590845</v>
       </c>
       <c r="B29" t="n">
-        <v>79726</v>
+        <v>91996</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3604,30 +3604,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730829</v>
+        <v>730764</v>
       </c>
       <c r="R29" t="n">
-        <v>7358728</v>
+        <v>7358768</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3672,11 +3672,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3703,10 +3698,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121590884</v>
+        <v>121590843</v>
       </c>
       <c r="B30" t="n">
-        <v>92029</v>
+        <v>79726</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3715,30 +3710,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3100</v>
+        <v>6462</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3747,10 +3742,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730767</v>
+        <v>730936</v>
       </c>
       <c r="R30" t="n">
-        <v>7358759</v>
+        <v>7358694</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3783,6 +3778,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3809,10 +3809,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121590872</v>
+        <v>121590855</v>
       </c>
       <c r="B31" t="n">
-        <v>91998</v>
+        <v>79732</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3821,30 +3821,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>6463</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3853,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730741</v>
+        <v>730855</v>
       </c>
       <c r="R31" t="n">
-        <v>7358824</v>
+        <v>7358731</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3889,6 +3889,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3915,10 +3920,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121590840</v>
+        <v>121590861</v>
       </c>
       <c r="B32" t="n">
-        <v>97067</v>
+        <v>92032</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3927,30 +3932,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>5449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3959,10 +3964,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>731001</v>
+        <v>730810</v>
       </c>
       <c r="R32" t="n">
-        <v>7358693</v>
+        <v>7358795</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4021,10 +4026,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121590834</v>
+        <v>121590882</v>
       </c>
       <c r="B33" t="n">
-        <v>57373</v>
+        <v>91998</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4037,26 +4042,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4065,10 +4070,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>731015</v>
+        <v>730749</v>
       </c>
       <c r="R33" t="n">
-        <v>7358724</v>
+        <v>7358805</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4101,11 +4106,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Födosökshack i tallöverståndare</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4132,10 +4132,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121590883</v>
+        <v>121590838</v>
       </c>
       <c r="B34" t="n">
-        <v>92032</v>
+        <v>82400</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4148,26 +4148,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>1312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730758</v>
+        <v>730995</v>
       </c>
       <c r="R34" t="n">
-        <v>7358773</v>
+        <v>7358751</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4238,10 +4238,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121590839</v>
+        <v>121590871</v>
       </c>
       <c r="B35" t="n">
-        <v>78616</v>
+        <v>79205</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4254,21 +4254,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4282,10 +4282,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>731001</v>
+        <v>730758</v>
       </c>
       <c r="R35" t="n">
-        <v>7358729</v>
+        <v>7358818</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4322,7 +4322,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Mindre ex på en gammal gran</t>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4349,10 +4349,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121590866</v>
+        <v>121590873</v>
       </c>
       <c r="B36" t="n">
-        <v>78352</v>
+        <v>92020</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4365,26 +4365,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>2059</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730818</v>
+        <v>730737</v>
       </c>
       <c r="R36" t="n">
-        <v>7358836</v>
+        <v>7358829</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4429,11 +4429,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4460,10 +4455,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121590836</v>
+        <v>121590879</v>
       </c>
       <c r="B37" t="n">
-        <v>79726</v>
+        <v>92020</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4472,30 +4467,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>2059</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4504,10 +4499,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730893</v>
+        <v>730730</v>
       </c>
       <c r="R37" t="n">
-        <v>7358778</v>
+        <v>7358824</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4540,11 +4535,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4571,10 +4561,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121590863</v>
+        <v>121590876</v>
       </c>
       <c r="B38" t="n">
-        <v>97073</v>
+        <v>92016</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4587,21 +4577,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221941</v>
+        <v>4366</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4615,10 +4605,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730859</v>
+        <v>730724</v>
       </c>
       <c r="R38" t="n">
-        <v>7358837</v>
+        <v>7358834</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4677,10 +4667,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121590835</v>
+        <v>121590870</v>
       </c>
       <c r="B39" t="n">
-        <v>79733</v>
+        <v>77548</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4689,25 +4679,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6464</v>
+        <v>6487</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4721,10 +4711,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730890</v>
+        <v>730756</v>
       </c>
       <c r="R39" t="n">
-        <v>7358797</v>
+        <v>7358818</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4761,7 +4751,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4788,10 +4778,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121590859</v>
+        <v>121590839</v>
       </c>
       <c r="B40" t="n">
-        <v>77548</v>
+        <v>78616</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4804,21 +4794,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4832,7 +4822,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730851</v>
+        <v>731001</v>
       </c>
       <c r="R40" t="n">
         <v>7358729</v>
@@ -4872,7 +4862,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På grov gammal kolad tallhögstubbe</t>
+          <t>Mindre ex på en gammal gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4899,10 +4889,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121590869</v>
+        <v>121590880</v>
       </c>
       <c r="B41" t="n">
-        <v>78000</v>
+        <v>92004</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4911,25 +4901,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4943,10 +4933,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730756</v>
+        <v>730731</v>
       </c>
       <c r="R41" t="n">
-        <v>7358818</v>
+        <v>7358821</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4979,11 +4969,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5010,10 +4995,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121590881</v>
+        <v>121590869</v>
       </c>
       <c r="B42" t="n">
-        <v>89403</v>
+        <v>78000</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5022,25 +5007,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6276</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5054,10 +5039,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730733</v>
+        <v>730756</v>
       </c>
       <c r="R42" t="n">
-        <v>7358825</v>
+        <v>7358818</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5090,6 +5075,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5116,10 +5106,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121590842</v>
+        <v>121590852</v>
       </c>
       <c r="B43" t="n">
-        <v>91290</v>
+        <v>79726</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5128,25 +5118,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>760</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5160,10 +5150,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730938</v>
+        <v>730829</v>
       </c>
       <c r="R43" t="n">
-        <v>7358696</v>
+        <v>7358728</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5200,7 +5190,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5227,10 +5217,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121590848</v>
+        <v>121590860</v>
       </c>
       <c r="B44" t="n">
-        <v>92029</v>
+        <v>78352</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5243,21 +5233,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3100</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5271,10 +5261,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>730804</v>
+        <v>730824</v>
       </c>
       <c r="R44" t="n">
-        <v>7358743</v>
+        <v>7358748</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5307,6 +5297,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På grov gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5333,10 +5328,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121590871</v>
+        <v>121590837</v>
       </c>
       <c r="B45" t="n">
-        <v>79205</v>
+        <v>90746</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5349,21 +5344,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5377,10 +5372,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>730758</v>
+        <v>730955</v>
       </c>
       <c r="R45" t="n">
-        <v>7358818</v>
+        <v>7358774</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5417,7 +5412,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
+          <t>På granhögstubbe och -låga</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5444,10 +5439,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121590846</v>
+        <v>121590834</v>
       </c>
       <c r="B46" t="n">
-        <v>92029</v>
+        <v>57373</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5460,26 +5455,26 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3100</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5488,10 +5483,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>730810</v>
+        <v>731015</v>
       </c>
       <c r="R46" t="n">
-        <v>7358754</v>
+        <v>7358724</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5524,6 +5519,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Födosökshack i tallöverståndare</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121590849</v>
+        <v>121590863</v>
       </c>
       <c r="B47" t="n">
-        <v>91998</v>
+        <v>97073</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5562,30 +5562,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5594,10 +5594,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730804</v>
+        <v>730859</v>
       </c>
       <c r="R47" t="n">
-        <v>7358743</v>
+        <v>7358837</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>

--- a/artfynd/A 71374-2021 artfynd.xlsx
+++ b/artfynd/A 71374-2021 artfynd.xlsx
@@ -1326,7 +1326,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121590849</v>
+        <v>121590851</v>
       </c>
       <c r="B8" t="n">
         <v>91998</v>
@@ -1370,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730804</v>
+        <v>730803</v>
       </c>
       <c r="R8" t="n">
-        <v>7358743</v>
+        <v>7358733</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,7 +1432,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121590851</v>
+        <v>121590849</v>
       </c>
       <c r="B9" t="n">
         <v>91998</v>
@@ -1476,10 +1476,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730803</v>
+        <v>730804</v>
       </c>
       <c r="R9" t="n">
-        <v>7358733</v>
+        <v>7358743</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1538,10 +1538,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121590848</v>
+        <v>121590859</v>
       </c>
       <c r="B10" t="n">
-        <v>92029</v>
+        <v>77548</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1554,21 +1554,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3100</v>
+        <v>6487</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1582,10 +1582,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730804</v>
+        <v>730851</v>
       </c>
       <c r="R10" t="n">
-        <v>7358743</v>
+        <v>7358729</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1618,6 +1618,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På grov gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121590868</v>
+        <v>121590848</v>
       </c>
       <c r="B12" t="n">
-        <v>79234</v>
+        <v>92029</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1766,21 +1771,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>3100</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1794,10 +1799,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730799</v>
+        <v>730804</v>
       </c>
       <c r="R12" t="n">
-        <v>7358812</v>
+        <v>7358743</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1830,11 +1835,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,10 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121590859</v>
+        <v>121590868</v>
       </c>
       <c r="B13" t="n">
-        <v>77548</v>
+        <v>79234</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,21 +1877,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730851</v>
+        <v>730799</v>
       </c>
       <c r="R13" t="n">
-        <v>7358729</v>
+        <v>7358812</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På grov gammal kolad tallhögstubbe</t>
+          <t>På gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2618,10 +2618,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121590846</v>
+        <v>121590842</v>
       </c>
       <c r="B20" t="n">
-        <v>92029</v>
+        <v>91290</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2630,30 +2630,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3100</v>
+        <v>760</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2662,10 +2662,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730810</v>
+        <v>730938</v>
       </c>
       <c r="R20" t="n">
-        <v>7358754</v>
+        <v>7358696</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2698,6 +2698,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2724,10 +2729,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121590842</v>
+        <v>121590846</v>
       </c>
       <c r="B21" t="n">
-        <v>91290</v>
+        <v>92029</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2736,30 +2741,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>760</v>
+        <v>3100</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2768,10 +2773,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730938</v>
+        <v>730810</v>
       </c>
       <c r="R21" t="n">
-        <v>7358696</v>
+        <v>7358754</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2804,11 +2809,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121590844</v>
+        <v>121590885</v>
       </c>
       <c r="B22" t="n">
-        <v>79733</v>
+        <v>92016</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2851,26 +2851,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6464</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730907</v>
+        <v>730757</v>
       </c>
       <c r="R22" t="n">
-        <v>7358717</v>
+        <v>7358754</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2915,11 +2915,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2946,7 +2941,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121590835</v>
+        <v>121590844</v>
       </c>
       <c r="B23" t="n">
         <v>79733</v>
@@ -2990,10 +2985,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730890</v>
+        <v>730907</v>
       </c>
       <c r="R23" t="n">
-        <v>7358797</v>
+        <v>7358717</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3057,10 +3052,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121590885</v>
+        <v>121590835</v>
       </c>
       <c r="B24" t="n">
-        <v>92016</v>
+        <v>79733</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3073,26 +3068,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4366</v>
+        <v>6464</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3101,10 +3096,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730757</v>
+        <v>730890</v>
       </c>
       <c r="R24" t="n">
-        <v>7358754</v>
+        <v>7358797</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3137,6 +3132,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3375,10 +3375,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121590872</v>
+        <v>121590866</v>
       </c>
       <c r="B27" t="n">
-        <v>91998</v>
+        <v>78352</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3391,26 +3391,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3419,10 +3419,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730741</v>
+        <v>730818</v>
       </c>
       <c r="R27" t="n">
-        <v>7358824</v>
+        <v>7358836</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3455,6 +3455,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3481,10 +3486,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121590866</v>
+        <v>121590872</v>
       </c>
       <c r="B28" t="n">
-        <v>78352</v>
+        <v>91998</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3497,26 +3502,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3525,10 +3530,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730818</v>
+        <v>730741</v>
       </c>
       <c r="R28" t="n">
-        <v>7358836</v>
+        <v>7358824</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3561,11 +3566,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3698,10 +3698,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121590843</v>
+        <v>121590861</v>
       </c>
       <c r="B30" t="n">
-        <v>79726</v>
+        <v>92032</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3710,30 +3710,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6462</v>
+        <v>5449</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730936</v>
+        <v>730810</v>
       </c>
       <c r="R30" t="n">
-        <v>7358694</v>
+        <v>7358795</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3778,11 +3778,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3809,10 +3804,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121590855</v>
+        <v>121590843</v>
       </c>
       <c r="B31" t="n">
-        <v>79732</v>
+        <v>79726</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3825,21 +3820,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3853,10 +3848,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730855</v>
+        <v>730936</v>
       </c>
       <c r="R31" t="n">
-        <v>7358731</v>
+        <v>7358694</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3893,7 +3888,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3920,10 +3915,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121590861</v>
+        <v>121590855</v>
       </c>
       <c r="B32" t="n">
-        <v>92032</v>
+        <v>79732</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3932,30 +3927,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>6463</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3964,10 +3959,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730810</v>
+        <v>730855</v>
       </c>
       <c r="R32" t="n">
-        <v>7358795</v>
+        <v>7358731</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4000,6 +3995,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4026,10 +4026,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121590882</v>
+        <v>121590838</v>
       </c>
       <c r="B33" t="n">
-        <v>91998</v>
+        <v>82400</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4042,26 +4042,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4362</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730749</v>
+        <v>730995</v>
       </c>
       <c r="R33" t="n">
-        <v>7358805</v>
+        <v>7358751</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4132,10 +4132,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121590838</v>
+        <v>121590882</v>
       </c>
       <c r="B34" t="n">
-        <v>82400</v>
+        <v>91998</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4148,26 +4148,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4176,10 +4176,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730995</v>
+        <v>730749</v>
       </c>
       <c r="R34" t="n">
-        <v>7358751</v>
+        <v>7358805</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -5439,10 +5439,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121590834</v>
+        <v>121590857</v>
       </c>
       <c r="B46" t="n">
-        <v>57373</v>
+        <v>79601</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5451,25 +5451,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6456</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5483,10 +5483,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>731015</v>
+        <v>730854</v>
       </c>
       <c r="R46" t="n">
-        <v>7358724</v>
+        <v>7358725</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Födosökshack i tallöverståndare</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121590863</v>
+        <v>121590834</v>
       </c>
       <c r="B47" t="n">
-        <v>97073</v>
+        <v>57373</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5562,25 +5562,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5594,10 +5594,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>730859</v>
+        <v>731015</v>
       </c>
       <c r="R47" t="n">
-        <v>7358837</v>
+        <v>7358724</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5630,6 +5630,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Födosökshack i tallöverståndare</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5656,10 +5661,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121590857</v>
+        <v>121590863</v>
       </c>
       <c r="B48" t="n">
-        <v>79601</v>
+        <v>97073</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5672,21 +5677,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>221941</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5700,10 +5705,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730854</v>
+        <v>730859</v>
       </c>
       <c r="R48" t="n">
-        <v>7358725</v>
+        <v>7358837</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5736,11 +5741,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 71374-2021 artfynd.xlsx
+++ b/artfynd/A 71374-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121590881</v>
+        <v>121590866</v>
       </c>
       <c r="B2" t="n">
-        <v>89403</v>
+        <v>78352</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6276</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730733</v>
+        <v>730818</v>
       </c>
       <c r="R2" t="n">
-        <v>7358825</v>
+        <v>7358836</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -755,6 +755,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121590836</v>
+        <v>121590854</v>
       </c>
       <c r="B3" t="n">
-        <v>79726</v>
+        <v>79698</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +798,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -825,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730893</v>
+        <v>730828</v>
       </c>
       <c r="R3" t="n">
-        <v>7358778</v>
+        <v>7358733</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121590877</v>
+        <v>121590842</v>
       </c>
       <c r="B4" t="n">
-        <v>91998</v>
+        <v>91290</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,30 +909,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>760</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -936,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>730725</v>
+        <v>730938</v>
       </c>
       <c r="R4" t="n">
-        <v>7358827</v>
+        <v>7358696</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,6 +977,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121590858</v>
+        <v>121590851</v>
       </c>
       <c r="B5" t="n">
-        <v>79726</v>
+        <v>91998</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,30 +1020,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1042,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730856</v>
+        <v>730803</v>
       </c>
       <c r="R5" t="n">
-        <v>7358724</v>
+        <v>7358733</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1078,11 +1088,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121590850</v>
+        <v>121590834</v>
       </c>
       <c r="B6" t="n">
-        <v>92004</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1121,30 +1126,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1153,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>730806</v>
+        <v>731015</v>
       </c>
       <c r="R6" t="n">
-        <v>7358740</v>
+        <v>7358724</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1189,6 +1194,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Födosökshack i tallöverståndare</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121590853</v>
+        <v>121590848</v>
       </c>
       <c r="B7" t="n">
-        <v>79733</v>
+        <v>92029</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1237,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>3100</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1259,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730825</v>
+        <v>730804</v>
       </c>
       <c r="R7" t="n">
-        <v>7358734</v>
+        <v>7358743</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1295,11 +1305,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,7 +1331,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121590851</v>
+        <v>121590847</v>
       </c>
       <c r="B8" t="n">
         <v>91998</v>
@@ -1361,7 +1366,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1370,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730803</v>
+        <v>730811</v>
       </c>
       <c r="R8" t="n">
-        <v>7358733</v>
+        <v>7358748</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,10 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121590849</v>
+        <v>121590855</v>
       </c>
       <c r="B9" t="n">
-        <v>91998</v>
+        <v>79732</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,30 +1449,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>6463</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1476,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>730804</v>
+        <v>730855</v>
       </c>
       <c r="R9" t="n">
-        <v>7358743</v>
+        <v>7358731</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1512,6 +1517,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1538,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121590859</v>
+        <v>121590885</v>
       </c>
       <c r="B10" t="n">
-        <v>77548</v>
+        <v>92016</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1550,30 +1560,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6487</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1582,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730851</v>
+        <v>730757</v>
       </c>
       <c r="R10" t="n">
-        <v>7358729</v>
+        <v>7358754</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1618,11 +1628,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På grov gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1649,10 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121590856</v>
+        <v>121590877</v>
       </c>
       <c r="B11" t="n">
-        <v>97067</v>
+        <v>91998</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1661,30 +1666,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1693,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730873</v>
+        <v>730725</v>
       </c>
       <c r="R11" t="n">
-        <v>7358715</v>
+        <v>7358827</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1755,10 +1760,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121590848</v>
+        <v>121590860</v>
       </c>
       <c r="B12" t="n">
-        <v>92029</v>
+        <v>78352</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1771,21 +1776,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3100</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1799,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730804</v>
+        <v>730824</v>
       </c>
       <c r="R12" t="n">
-        <v>7358743</v>
+        <v>7358748</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1835,6 +1840,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På grov gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1861,10 +1871,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121590868</v>
+        <v>121590844</v>
       </c>
       <c r="B13" t="n">
-        <v>79234</v>
+        <v>79733</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1873,25 +1883,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1905,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730799</v>
+        <v>730907</v>
       </c>
       <c r="R13" t="n">
-        <v>7358812</v>
+        <v>7358717</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1945,7 +1955,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På gammal kolad tallstubbe</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1972,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121590883</v>
+        <v>121590864</v>
       </c>
       <c r="B14" t="n">
-        <v>92032</v>
+        <v>92004</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1984,30 +1994,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2016,10 +2026,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730758</v>
+        <v>730835</v>
       </c>
       <c r="R14" t="n">
-        <v>7358773</v>
+        <v>7358839</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2078,10 +2088,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121590854</v>
+        <v>121590863</v>
       </c>
       <c r="B15" t="n">
-        <v>79698</v>
+        <v>97073</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,25 +2100,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2122,10 +2132,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730828</v>
+        <v>730859</v>
       </c>
       <c r="R15" t="n">
-        <v>7358733</v>
+        <v>7358837</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2158,11 +2168,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2189,10 +2194,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121590847</v>
+        <v>121590840</v>
       </c>
       <c r="B16" t="n">
-        <v>91998</v>
+        <v>97067</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2201,30 +2206,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4362</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2233,10 +2238,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730811</v>
+        <v>731001</v>
       </c>
       <c r="R16" t="n">
-        <v>7358748</v>
+        <v>7358693</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2295,10 +2300,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121590841</v>
+        <v>121590849</v>
       </c>
       <c r="B17" t="n">
-        <v>82400</v>
+        <v>91998</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2311,26 +2316,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2339,10 +2344,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730998</v>
+        <v>730804</v>
       </c>
       <c r="R17" t="n">
-        <v>7358696</v>
+        <v>7358743</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2375,11 +2380,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,10 +2406,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121590864</v>
+        <v>121590836</v>
       </c>
       <c r="B18" t="n">
-        <v>92004</v>
+        <v>79726</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2422,26 +2422,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730835</v>
+        <v>730893</v>
       </c>
       <c r="R18" t="n">
-        <v>7358839</v>
+        <v>7358778</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2486,6 +2486,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2512,10 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121590874</v>
+        <v>121590859</v>
       </c>
       <c r="B19" t="n">
-        <v>91998</v>
+        <v>77548</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2528,26 +2533,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4362</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2556,10 +2561,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730724</v>
+        <v>730851</v>
       </c>
       <c r="R19" t="n">
-        <v>7358840</v>
+        <v>7358729</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2592,6 +2597,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På grov gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2618,10 +2628,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121590842</v>
+        <v>121590839</v>
       </c>
       <c r="B20" t="n">
-        <v>91290</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2630,25 +2640,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>760</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2662,10 +2672,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730938</v>
+        <v>731001</v>
       </c>
       <c r="R20" t="n">
-        <v>7358696</v>
+        <v>7358729</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2702,7 +2712,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Mindre ex på en gammal gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2729,7 +2739,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121590846</v>
+        <v>121590884</v>
       </c>
       <c r="B21" t="n">
         <v>92029</v>
@@ -2764,7 +2774,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2773,10 +2783,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730810</v>
+        <v>730767</v>
       </c>
       <c r="R21" t="n">
-        <v>7358754</v>
+        <v>7358759</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2835,10 +2845,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121590885</v>
+        <v>121590845</v>
       </c>
       <c r="B22" t="n">
-        <v>92016</v>
+        <v>91996</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2847,30 +2857,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2879,10 +2889,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730757</v>
+        <v>730764</v>
       </c>
       <c r="R22" t="n">
-        <v>7358754</v>
+        <v>7358768</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2941,10 +2951,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121590844</v>
+        <v>121590881</v>
       </c>
       <c r="B23" t="n">
-        <v>79733</v>
+        <v>89403</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2953,25 +2963,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6464</v>
+        <v>6276</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2985,10 +2995,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>730907</v>
+        <v>730733</v>
       </c>
       <c r="R23" t="n">
-        <v>7358717</v>
+        <v>7358825</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3021,11 +3031,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,10 +3057,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121590835</v>
+        <v>121590880</v>
       </c>
       <c r="B24" t="n">
-        <v>79733</v>
+        <v>92004</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3068,21 +3073,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6464</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3096,10 +3101,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730890</v>
+        <v>730731</v>
       </c>
       <c r="R24" t="n">
-        <v>7358797</v>
+        <v>7358821</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3132,11 +3137,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3163,10 +3163,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121590840</v>
+        <v>121590872</v>
       </c>
       <c r="B25" t="n">
-        <v>97067</v>
+        <v>91998</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3175,30 +3175,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>731001</v>
+        <v>730741</v>
       </c>
       <c r="R25" t="n">
-        <v>7358693</v>
+        <v>7358824</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3269,10 +3269,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121590884</v>
+        <v>121590858</v>
       </c>
       <c r="B26" t="n">
-        <v>92029</v>
+        <v>79726</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3281,30 +3281,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3100</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730767</v>
+        <v>730856</v>
       </c>
       <c r="R26" t="n">
-        <v>7358759</v>
+        <v>7358724</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3349,6 +3349,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3375,10 +3380,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121590866</v>
+        <v>121590853</v>
       </c>
       <c r="B27" t="n">
-        <v>78352</v>
+        <v>79733</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3387,25 +3392,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6464</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3419,10 +3424,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730818</v>
+        <v>730825</v>
       </c>
       <c r="R27" t="n">
-        <v>7358836</v>
+        <v>7358734</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3459,7 +3464,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal kolad tallhögstubbe</t>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3486,10 +3491,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121590872</v>
+        <v>121590856</v>
       </c>
       <c r="B28" t="n">
-        <v>91998</v>
+        <v>97067</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3498,30 +3503,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4362</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3530,10 +3535,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730741</v>
+        <v>730873</v>
       </c>
       <c r="R28" t="n">
-        <v>7358824</v>
+        <v>7358715</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3592,10 +3597,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121590845</v>
+        <v>121590882</v>
       </c>
       <c r="B29" t="n">
-        <v>91996</v>
+        <v>91998</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3608,26 +3613,26 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3636,10 +3641,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730764</v>
+        <v>730749</v>
       </c>
       <c r="R29" t="n">
-        <v>7358768</v>
+        <v>7358805</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3698,10 +3703,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121590861</v>
+        <v>121590876</v>
       </c>
       <c r="B30" t="n">
-        <v>92032</v>
+        <v>92016</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3710,30 +3715,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3742,10 +3747,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730810</v>
+        <v>730724</v>
       </c>
       <c r="R30" t="n">
-        <v>7358795</v>
+        <v>7358834</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3804,10 +3809,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121590843</v>
+        <v>121590861</v>
       </c>
       <c r="B31" t="n">
-        <v>79726</v>
+        <v>92032</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3816,30 +3821,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>5449</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3848,10 +3853,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730936</v>
+        <v>730810</v>
       </c>
       <c r="R31" t="n">
-        <v>7358694</v>
+        <v>7358795</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3884,11 +3889,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3915,10 +3915,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121590855</v>
+        <v>121590870</v>
       </c>
       <c r="B32" t="n">
-        <v>79732</v>
+        <v>77548</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3927,25 +3927,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6463</v>
+        <v>6487</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3959,10 +3959,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730855</v>
+        <v>730756</v>
       </c>
       <c r="R32" t="n">
-        <v>7358731</v>
+        <v>7358818</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3999,7 +3999,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På död sälg</t>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4026,10 +4026,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121590838</v>
+        <v>121590868</v>
       </c>
       <c r="B33" t="n">
-        <v>82400</v>
+        <v>79234</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4042,21 +4042,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1312</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730995</v>
+        <v>730799</v>
       </c>
       <c r="R33" t="n">
-        <v>7358751</v>
+        <v>7358812</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4106,6 +4106,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4132,10 +4137,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121590882</v>
+        <v>121590879</v>
       </c>
       <c r="B34" t="n">
-        <v>91998</v>
+        <v>92020</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4148,26 +4153,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4176,10 +4181,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730749</v>
+        <v>730730</v>
       </c>
       <c r="R34" t="n">
-        <v>7358805</v>
+        <v>7358824</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4238,10 +4243,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121590871</v>
+        <v>121590850</v>
       </c>
       <c r="B35" t="n">
-        <v>79205</v>
+        <v>92004</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4250,30 +4255,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4282,10 +4287,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730758</v>
+        <v>730806</v>
       </c>
       <c r="R35" t="n">
-        <v>7358818</v>
+        <v>7358740</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4318,11 +4323,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4349,10 +4349,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121590873</v>
+        <v>121590857</v>
       </c>
       <c r="B36" t="n">
-        <v>92020</v>
+        <v>79601</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4361,30 +4361,30 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2059</v>
+        <v>6456</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4393,10 +4393,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>730737</v>
+        <v>730854</v>
       </c>
       <c r="R36" t="n">
-        <v>7358829</v>
+        <v>7358725</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4429,6 +4429,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4455,10 +4460,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121590879</v>
+        <v>121590835</v>
       </c>
       <c r="B37" t="n">
-        <v>92020</v>
+        <v>79733</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4467,30 +4472,30 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2059</v>
+        <v>6464</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4499,10 +4504,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>730730</v>
+        <v>730890</v>
       </c>
       <c r="R37" t="n">
-        <v>7358824</v>
+        <v>7358797</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4535,6 +4540,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4561,10 +4571,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121590876</v>
+        <v>121590843</v>
       </c>
       <c r="B38" t="n">
-        <v>92016</v>
+        <v>79726</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4577,21 +4587,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4366</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4605,10 +4615,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>730724</v>
+        <v>730936</v>
       </c>
       <c r="R38" t="n">
-        <v>7358834</v>
+        <v>7358694</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4641,6 +4651,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4667,10 +4682,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121590870</v>
+        <v>121590852</v>
       </c>
       <c r="B39" t="n">
-        <v>77548</v>
+        <v>79726</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4679,25 +4694,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6487</v>
+        <v>6462</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4711,10 +4726,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730756</v>
+        <v>730829</v>
       </c>
       <c r="R39" t="n">
-        <v>7358818</v>
+        <v>7358728</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4751,7 +4766,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4778,10 +4793,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121590839</v>
+        <v>121590871</v>
       </c>
       <c r="B40" t="n">
-        <v>78616</v>
+        <v>79205</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4794,21 +4809,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4822,10 +4837,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>731001</v>
+        <v>730758</v>
       </c>
       <c r="R40" t="n">
-        <v>7358729</v>
+        <v>7358818</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4862,7 +4877,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Mindre ex på en gammal gran</t>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4889,10 +4904,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121590880</v>
+        <v>121590841</v>
       </c>
       <c r="B41" t="n">
-        <v>92004</v>
+        <v>82400</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4901,25 +4916,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4933,10 +4948,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730731</v>
+        <v>730998</v>
       </c>
       <c r="R41" t="n">
-        <v>7358821</v>
+        <v>7358696</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4969,6 +4984,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4995,10 +5015,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121590869</v>
+        <v>121590838</v>
       </c>
       <c r="B42" t="n">
-        <v>78000</v>
+        <v>82400</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5011,21 +5031,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6437</v>
+        <v>1312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5039,10 +5059,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730756</v>
+        <v>730995</v>
       </c>
       <c r="R42" t="n">
-        <v>7358818</v>
+        <v>7358751</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5075,11 +5095,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5106,10 +5121,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121590852</v>
+        <v>121590874</v>
       </c>
       <c r="B43" t="n">
-        <v>79726</v>
+        <v>91998</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5118,30 +5133,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6462</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5150,10 +5165,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730829</v>
+        <v>730724</v>
       </c>
       <c r="R43" t="n">
-        <v>7358728</v>
+        <v>7358840</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5186,11 +5201,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5217,10 +5227,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121590860</v>
+        <v>121590846</v>
       </c>
       <c r="B44" t="n">
-        <v>78352</v>
+        <v>92029</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5233,26 +5243,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>3100</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5261,10 +5271,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>730824</v>
+        <v>730810</v>
       </c>
       <c r="R44" t="n">
-        <v>7358748</v>
+        <v>7358754</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5297,11 +5307,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På grov gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5439,10 +5444,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121590857</v>
+        <v>121590883</v>
       </c>
       <c r="B46" t="n">
-        <v>79601</v>
+        <v>92032</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5451,30 +5456,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6456</v>
+        <v>5449</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5483,10 +5488,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>730854</v>
+        <v>730758</v>
       </c>
       <c r="R46" t="n">
-        <v>7358725</v>
+        <v>7358773</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5519,11 +5524,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5550,10 +5550,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121590834</v>
+        <v>121590873</v>
       </c>
       <c r="B47" t="n">
-        <v>57373</v>
+        <v>92020</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5566,26 +5566,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>2059</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5594,10 +5594,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>731015</v>
+        <v>730737</v>
       </c>
       <c r="R47" t="n">
-        <v>7358724</v>
+        <v>7358829</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5630,11 +5630,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Födosökshack i tallöverståndare</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5661,10 +5656,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121590863</v>
+        <v>121590869</v>
       </c>
       <c r="B48" t="n">
-        <v>97073</v>
+        <v>78000</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5673,25 +5668,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221941</v>
+        <v>6437</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5705,10 +5700,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>730859</v>
+        <v>730756</v>
       </c>
       <c r="R48" t="n">
-        <v>7358837</v>
+        <v>7358818</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5741,6 +5736,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 71374-2021 artfynd.xlsx
+++ b/artfynd/A 71374-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121590860</v>
+        <v>121590842</v>
       </c>
       <c r="B2" t="n">
-        <v>78365</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>730824</v>
+        <v>730938</v>
       </c>
       <c r="R2" t="n">
-        <v>7358748</v>
+        <v>7358696</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +754,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På grov gammal kolad tallstubbe</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121590863</v>
+        <v>121590838</v>
       </c>
       <c r="B3" t="n">
-        <v>97091</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>730859</v>
+        <v>730995</v>
       </c>
       <c r="R3" t="n">
-        <v>7358837</v>
+        <v>7358751</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -895,12 +885,7 @@
         <v>121590841</v>
       </c>
       <c r="B4" t="n">
-        <v>82414</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1003,15 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121590881</v>
+        <v>121590873</v>
       </c>
       <c r="B5" t="n">
-        <v>89417</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,26 +999,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1047,10 +1027,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>730733</v>
+        <v>730737</v>
       </c>
       <c r="R5" t="n">
-        <v>7358825</v>
+        <v>7358829</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1109,42 +1089,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121590839</v>
+        <v>121590879</v>
       </c>
       <c r="B6" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1153,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>731001</v>
+        <v>730730</v>
       </c>
       <c r="R6" t="n">
-        <v>7358729</v>
+        <v>7358824</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1189,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Mindre ex på en gammal gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,37 +1190,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121590853</v>
+        <v>121590854</v>
       </c>
       <c r="B7" t="n">
-        <v>79746</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1264,10 +1229,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>730825</v>
+        <v>730828</v>
       </c>
       <c r="R7" t="n">
-        <v>7358734</v>
+        <v>7358733</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1331,42 +1296,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121590856</v>
+        <v>121590846</v>
       </c>
       <c r="B8" t="n">
-        <v>97085</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>3100</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1375,10 +1335,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>730873</v>
+        <v>730810</v>
       </c>
       <c r="R8" t="n">
-        <v>7358715</v>
+        <v>7358754</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1437,15 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121590849</v>
+        <v>121590848</v>
       </c>
       <c r="B9" t="n">
-        <v>92012</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1453,26 +1408,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4362</v>
+        <v>3100</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1543,42 +1498,37 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121590855</v>
+        <v>121590884</v>
       </c>
       <c r="B10" t="n">
-        <v>79745</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6463</v>
+        <v>3100</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1587,10 +1537,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>730855</v>
+        <v>730767</v>
       </c>
       <c r="R10" t="n">
-        <v>7358731</v>
+        <v>7358759</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1623,11 +1573,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1654,15 +1599,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121590848</v>
+        <v>121590845</v>
       </c>
       <c r="B11" t="n">
-        <v>92043</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1670,26 +1610,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3100</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1698,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>730804</v>
+        <v>730764</v>
       </c>
       <c r="R11" t="n">
-        <v>7358743</v>
+        <v>7358768</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1760,15 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121590879</v>
+        <v>121590847</v>
       </c>
       <c r="B12" t="n">
-        <v>92034</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1776,26 +1711,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1804,10 +1739,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>730730</v>
+        <v>730811</v>
       </c>
       <c r="R12" t="n">
-        <v>7358824</v>
+        <v>7358748</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1866,15 +1801,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121590838</v>
+        <v>121590849</v>
       </c>
       <c r="B13" t="n">
-        <v>82414</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,26 +1812,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1312</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1910,10 +1840,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>730995</v>
+        <v>730804</v>
       </c>
       <c r="R13" t="n">
-        <v>7358751</v>
+        <v>7358743</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1972,42 +1902,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121590880</v>
+        <v>121590851</v>
       </c>
       <c r="B14" t="n">
-        <v>92018</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2016,10 +1941,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>730731</v>
+        <v>730803</v>
       </c>
       <c r="R14" t="n">
-        <v>7358821</v>
+        <v>7358733</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2078,15 +2003,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121590854</v>
+        <v>121590872</v>
       </c>
       <c r="B15" t="n">
-        <v>79711</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2094,26 +2014,26 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2081</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2122,10 +2042,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>730828</v>
+        <v>730741</v>
       </c>
       <c r="R15" t="n">
-        <v>7358733</v>
+        <v>7358824</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2158,11 +2078,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2189,15 +2104,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121590859</v>
+        <v>121590874</v>
       </c>
       <c r="B16" t="n">
-        <v>77561</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2205,26 +2115,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6487</v>
+        <v>4362</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2233,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>730851</v>
+        <v>730724</v>
       </c>
       <c r="R16" t="n">
-        <v>7358729</v>
+        <v>7358840</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2269,11 +2179,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På grov gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2300,15 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121590882</v>
+        <v>121590877</v>
       </c>
       <c r="B17" t="n">
-        <v>92012</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,7 +2235,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2344,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>730749</v>
+        <v>730725</v>
       </c>
       <c r="R17" t="n">
-        <v>7358805</v>
+        <v>7358827</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2406,15 +2306,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121590877</v>
+        <v>121590882</v>
       </c>
       <c r="B18" t="n">
-        <v>92012</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2441,7 +2336,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2450,10 +2345,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>730725</v>
+        <v>730749</v>
       </c>
       <c r="R18" t="n">
-        <v>7358827</v>
+        <v>7358805</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2512,42 +2407,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121590876</v>
+        <v>121590850</v>
       </c>
       <c r="B19" t="n">
-        <v>92030</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2556,10 +2446,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>730724</v>
+        <v>730806</v>
       </c>
       <c r="R19" t="n">
-        <v>7358834</v>
+        <v>7358740</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2618,15 +2508,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121590866</v>
+        <v>121590864</v>
       </c>
       <c r="B20" t="n">
-        <v>78365</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2634,26 +2519,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2662,10 +2547,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>730818</v>
+        <v>730835</v>
       </c>
       <c r="R20" t="n">
-        <v>7358836</v>
+        <v>7358839</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2698,11 +2583,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2729,37 +2609,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121590858</v>
+        <v>121590880</v>
       </c>
       <c r="B21" t="n">
-        <v>79739</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -2773,10 +2648,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>730856</v>
+        <v>730731</v>
       </c>
       <c r="R21" t="n">
-        <v>7358724</v>
+        <v>7358821</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2809,11 +2684,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2840,15 +2710,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121590847</v>
+        <v>121590876</v>
       </c>
       <c r="B22" t="n">
-        <v>92012</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2856,26 +2721,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2884,10 +2749,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>730811</v>
+        <v>730724</v>
       </c>
       <c r="R22" t="n">
-        <v>7358748</v>
+        <v>7358834</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2946,42 +2811,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121590840</v>
+        <v>121590885</v>
       </c>
       <c r="B23" t="n">
-        <v>97085</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>4366</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2990,10 +2850,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>731001</v>
+        <v>730757</v>
       </c>
       <c r="R23" t="n">
-        <v>7358693</v>
+        <v>7358754</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3052,37 +2912,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121590871</v>
+        <v>121590881</v>
       </c>
       <c r="B24" t="n">
-        <v>79218</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>6276</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3096,10 +2951,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>730758</v>
+        <v>730733</v>
       </c>
       <c r="R24" t="n">
-        <v>7358818</v>
+        <v>7358825</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3132,11 +2987,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3163,42 +3013,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121590883</v>
+        <v>121590839</v>
       </c>
       <c r="B25" t="n">
-        <v>92046</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3207,10 +3052,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>730758</v>
+        <v>731001</v>
       </c>
       <c r="R25" t="n">
-        <v>7358773</v>
+        <v>7358729</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3243,6 +3088,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Mindre ex på en gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3269,15 +3119,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121590846</v>
+        <v>121590869</v>
       </c>
       <c r="B26" t="n">
-        <v>92043</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3285,26 +3130,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3100</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3313,10 +3158,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>730810</v>
+        <v>730756</v>
       </c>
       <c r="R26" t="n">
-        <v>7358754</v>
+        <v>7358818</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3349,6 +3194,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3375,37 +3225,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121590842</v>
+        <v>121590860</v>
       </c>
       <c r="B27" t="n">
-        <v>91304</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>760</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3419,10 +3264,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>730938</v>
+        <v>730824</v>
       </c>
       <c r="R27" t="n">
-        <v>7358696</v>
+        <v>7358748</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3459,7 +3304,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På grov gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3486,37 +3331,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121590857</v>
+        <v>121590866</v>
       </c>
       <c r="B28" t="n">
-        <v>79614</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3530,10 +3370,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>730854</v>
+        <v>730818</v>
       </c>
       <c r="R28" t="n">
-        <v>7358725</v>
+        <v>7358836</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3570,7 +3410,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3597,37 +3437,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121590852</v>
+        <v>121590868</v>
       </c>
       <c r="B29" t="n">
-        <v>79739</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3641,10 +3476,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>730829</v>
+        <v>730799</v>
       </c>
       <c r="R29" t="n">
-        <v>7358728</v>
+        <v>7358812</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3681,7 +3516,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På grov sälg</t>
+          <t>På gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3708,37 +3543,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121590837</v>
+        <v>121590857</v>
       </c>
       <c r="B30" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3752,10 +3582,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>730955</v>
+        <v>730854</v>
       </c>
       <c r="R30" t="n">
-        <v>7358774</v>
+        <v>7358725</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3792,7 +3622,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På granhögstubbe och -låga</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3819,37 +3649,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121590870</v>
+        <v>121590836</v>
       </c>
       <c r="B31" t="n">
-        <v>77561</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6487</v>
+        <v>6462</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3863,10 +3688,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>730756</v>
+        <v>730893</v>
       </c>
       <c r="R31" t="n">
-        <v>7358818</v>
+        <v>7358778</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3903,7 +3728,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3930,42 +3755,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121590872</v>
+        <v>121590843</v>
       </c>
       <c r="B32" t="n">
-        <v>92012</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4362</v>
+        <v>6462</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3974,10 +3794,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>730741</v>
+        <v>730936</v>
       </c>
       <c r="R32" t="n">
-        <v>7358824</v>
+        <v>7358694</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4010,6 +3830,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4036,42 +3861,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121590884</v>
+        <v>121590852</v>
       </c>
       <c r="B33" t="n">
-        <v>92043</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3100</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4080,10 +3900,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>730767</v>
+        <v>730829</v>
       </c>
       <c r="R33" t="n">
-        <v>7358759</v>
+        <v>7358728</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4116,6 +3936,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4142,15 +3967,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121590843</v>
+        <v>121590858</v>
       </c>
       <c r="B34" t="n">
-        <v>79739</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4186,10 +4006,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>730936</v>
+        <v>730856</v>
       </c>
       <c r="R34" t="n">
-        <v>7358694</v>
+        <v>7358724</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4253,15 +4073,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121590885</v>
+        <v>121590855</v>
       </c>
       <c r="B35" t="n">
-        <v>92030</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4269,26 +4084,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4366</v>
+        <v>6463</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4297,10 +4112,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>730757</v>
+        <v>730855</v>
       </c>
       <c r="R35" t="n">
-        <v>7358754</v>
+        <v>7358731</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4333,6 +4148,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På död sälg</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4362,12 +4182,7 @@
         <v>121590835</v>
       </c>
       <c r="B36" t="n">
-        <v>79746</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4473,12 +4288,7 @@
         <v>121590844</v>
       </c>
       <c r="B37" t="n">
-        <v>79746</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4581,37 +4391,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121590834</v>
+        <v>121590853</v>
       </c>
       <c r="B38" t="n">
-        <v>57381</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4625,10 +4430,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>731015</v>
+        <v>730825</v>
       </c>
       <c r="R38" t="n">
-        <v>7358724</v>
+        <v>7358734</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4665,7 +4470,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Födosökshack i tallöverståndare</t>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4692,42 +4497,37 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121590850</v>
+        <v>121590859</v>
       </c>
       <c r="B39" t="n">
-        <v>92018</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -4736,10 +4536,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>730806</v>
+        <v>730851</v>
       </c>
       <c r="R39" t="n">
-        <v>7358740</v>
+        <v>7358729</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4772,6 +4572,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På grov gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4798,42 +4603,37 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121590864</v>
+        <v>121590870</v>
       </c>
       <c r="B40" t="n">
-        <v>92018</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -4842,10 +4642,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>730835</v>
+        <v>730756</v>
       </c>
       <c r="R40" t="n">
-        <v>7358839</v>
+        <v>7358818</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4878,6 +4678,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4904,42 +4709,37 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121590851</v>
+        <v>121590834</v>
       </c>
       <c r="B41" t="n">
-        <v>92012</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4362</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4948,10 +4748,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>730803</v>
+        <v>731015</v>
       </c>
       <c r="R41" t="n">
-        <v>7358733</v>
+        <v>7358724</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4984,6 +4784,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Födosökshack i tallöverståndare</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5010,42 +4815,37 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121590861</v>
+        <v>121590863</v>
       </c>
       <c r="B42" t="n">
-        <v>92046</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5449</v>
+        <v>221941</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5054,10 +4854,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>730810</v>
+        <v>730859</v>
       </c>
       <c r="R42" t="n">
-        <v>7358795</v>
+        <v>7358837</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5116,42 +4916,37 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121590845</v>
+        <v>121590840</v>
       </c>
       <c r="B43" t="n">
-        <v>92010</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4361</v>
+        <v>221945</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5160,10 +4955,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>730764</v>
+        <v>731001</v>
       </c>
       <c r="R43" t="n">
-        <v>7358768</v>
+        <v>7358693</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5222,37 +5017,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121590868</v>
+        <v>121590856</v>
       </c>
       <c r="B44" t="n">
-        <v>79247</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -5266,10 +5056,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>730799</v>
+        <v>730873</v>
       </c>
       <c r="R44" t="n">
-        <v>7358812</v>
+        <v>7358715</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5302,11 +5092,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På gammal kolad tallstubbe</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5333,15 +5118,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121590869</v>
+        <v>121590867</v>
       </c>
       <c r="B45" t="n">
-        <v>78013</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5349,21 +5129,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5377,10 +5157,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>730756</v>
+        <v>730815</v>
       </c>
       <c r="R45" t="n">
-        <v>7358818</v>
+        <v>7358838</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5417,7 +5197,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gammal tallhögstubbe med brandljud</t>
+          <t>På gammal kolad tallhögstubbe</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5444,37 +5224,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121590836</v>
+        <v>121590871</v>
       </c>
       <c r="B46" t="n">
-        <v>79739</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5488,10 +5263,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>730893</v>
+        <v>730758</v>
       </c>
       <c r="R46" t="n">
-        <v>7358778</v>
+        <v>7358818</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5528,7 +5303,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal tallhögstubbe med brandljud</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5552,218 +5327,6 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>121590873</v>
-      </c>
-      <c r="B47" t="n">
-        <v>92034</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>2059</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Skrovlig taggsvamp</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Hydnellum scabrosum</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>Jokkmokksmyran, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>730737</v>
-      </c>
-      <c r="R47" t="n">
-        <v>7358829</v>
-      </c>
-      <c r="S47" t="n">
-        <v>5</v>
-      </c>
-      <c r="T47" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="V47" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AD47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>121590874</v>
-      </c>
-      <c r="B48" t="n">
-        <v>92012</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>4362</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Hydnellum caeruleum</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>Jokkmokksmyran, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>730724</v>
-      </c>
-      <c r="R48" t="n">
-        <v>7358840</v>
-      </c>
-      <c r="S48" t="n">
-        <v>5</v>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="V48" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>Jokkmokk</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>2024-08-27</t>
-        </is>
-      </c>
-      <c r="AD48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>Amanda Tas</t>
-        </is>
-      </c>
-      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 71374-2021 artfynd.xlsx
+++ b/artfynd/A 71374-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AZ46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590842</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590838</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590841</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1086,6 +1106,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590873</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590879</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1293,6 +1323,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590854</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590846</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1495,6 +1535,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590848</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1596,6 +1641,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590884</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1697,6 +1747,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590845</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1798,6 +1853,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590847</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1899,6 +1959,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590849</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2000,6 +2065,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590851</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2101,6 +2171,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590872</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2202,6 +2277,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590874</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2303,6 +2383,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590877</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2404,6 +2489,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590882</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2505,6 +2595,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590850</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2606,6 +2701,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590864</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2707,6 +2807,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590880</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2808,6 +2913,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590876</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2909,6 +3019,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590885</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3010,6 +3125,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590881</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3116,6 +3236,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590839</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3222,6 +3347,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590869</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3328,6 +3458,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590860</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3434,6 +3569,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590866</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3540,6 +3680,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590868</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3646,6 +3791,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590857</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3752,6 +3902,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590836</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3858,6 +4013,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590843</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3964,6 +4124,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590852</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4070,6 +4235,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590858</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4176,6 +4346,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590855</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4282,6 +4457,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590835</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4388,6 +4568,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590844</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4494,6 +4679,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590853</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4600,6 +4790,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590859</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4706,6 +4901,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590870</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4812,6 +5012,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590834</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4913,6 +5118,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590863</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5014,6 +5224,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590840</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5115,6 +5330,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590856</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5221,6 +5441,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590867</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5327,8 +5552,60 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121590871</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>